--- a/iShares/iShares-costs.xlsx
+++ b/iShares/iShares-costs.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="27628"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="28526"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/7c741cee80ec8cf3/Financieel/IndexFondsenOnderzoek/KeuzeWelkIndexFonds/OnderzoekPerFonds/iShares/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1222" documentId="13_ncr:1_{A6ACE176-4C08-4AFF-ACEF-0847542540D3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{C2382118-BDB9-4115-9C55-B8D1C93D3D02}"/>
+  <xr:revisionPtr revIDLastSave="1223" documentId="13_ncr:1_{A6ACE176-4C08-4AFF-ACEF-0847542540D3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{840DF9AB-C7A3-409E-8E30-FE03E73C9DB5}"/>
   <bookViews>
-    <workbookView xWindow="25695" yWindow="0" windowWidth="26010" windowHeight="20985" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="51840" windowHeight="21120" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Aanames" sheetId="6" r:id="rId1"/>
@@ -25,7 +25,7 @@
     <sheet name="TrackingDifference" sheetId="5" r:id="rId10"/>
     <sheet name="Lending%" sheetId="13" r:id="rId11"/>
   </sheets>
-  <calcPr calcId="191029"/>
+  <calcPr calcId="191028"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -36,6 +36,9 @@
         <xcalcf:feature name="microsoft.com:Single"/>
         <xcalcf:feature name="microsoft.com:FV"/>
         <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
       </xcalcf:calcFeatures>
     </ext>
   </extLst>
@@ -101,7 +104,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="330" uniqueCount="152">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="299" uniqueCount="135">
   <si>
     <t>Transaction costs</t>
   </si>
@@ -427,27 +430,6 @@
     <t>EM</t>
   </si>
   <si>
-    <t>IWDA</t>
-  </si>
-  <si>
-    <t>EMIM</t>
-  </si>
-  <si>
-    <t>IEMS</t>
-  </si>
-  <si>
-    <t>WSML</t>
-  </si>
-  <si>
-    <t>IEMM</t>
-  </si>
-  <si>
-    <t>IEMA</t>
-  </si>
-  <si>
-    <t>IWVL</t>
-  </si>
-  <si>
     <t>iShares III plc</t>
   </si>
   <si>
@@ -508,24 +490,6 @@
     <t>Boekjaar anders dan kalenderjaar! Juni</t>
   </si>
   <si>
-    <t>juni</t>
-  </si>
-  <si>
-    <t>Wat</t>
-  </si>
-  <si>
-    <t>Waar zit het</t>
-  </si>
-  <si>
-    <t>Boekjaar</t>
-  </si>
-  <si>
-    <t>feb</t>
-  </si>
-  <si>
-    <t>mei</t>
-  </si>
-  <si>
     <t>2015-2022</t>
   </si>
   <si>
@@ -538,15 +502,6 @@
     <t>iShares II PLC</t>
   </si>
   <si>
-    <t>iShares MSCI World Islamic UCITS ETF</t>
-  </si>
-  <si>
-    <t>okt</t>
-  </si>
-  <si>
-    <t>jul</t>
-  </si>
-  <si>
     <t>iShares IWMO</t>
   </si>
   <si>
@@ -554,9 +509,6 @@
   </si>
   <si>
     <t>MSCI World Momentum Index (USD) NET</t>
-  </si>
-  <si>
-    <t>Laatste die ik heb</t>
   </si>
 </sst>
 </file>
@@ -564,12 +516,12 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="6">
-    <numFmt numFmtId="44" formatCode="_ &quot;€&quot;\ * #,##0.00_ ;_ &quot;€&quot;\ * \-#,##0.00_ ;_ &quot;€&quot;\ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="164" formatCode="_ &quot;€&quot;\ * #,##0_ ;_ &quot;€&quot;\ * \-#,##0_ ;_ &quot;€&quot;\ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="165" formatCode="0.000%"/>
-    <numFmt numFmtId="166" formatCode="0.0%"/>
-    <numFmt numFmtId="167" formatCode="_ [$€-413]\ * #,##0_ ;_ [$€-413]\ * \-#,##0_ ;_ [$€-413]\ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="164" formatCode="_ &quot;€&quot;\ * #,##0.00_ ;_ &quot;€&quot;\ * \-#,##0.00_ ;_ &quot;€&quot;\ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="165" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="166" formatCode="_ &quot;€&quot;\ * #,##0_ ;_ &quot;€&quot;\ * \-#,##0_ ;_ &quot;€&quot;\ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="167" formatCode="0.000%"/>
+    <numFmt numFmtId="168" formatCode="0.0%"/>
+    <numFmt numFmtId="169" formatCode="_ [$€-413]\ * #,##0_ ;_ [$€-413]\ * \-#,##0_ ;_ [$€-413]\ * &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
   <fonts count="12" x14ac:knownFonts="1">
     <font>
@@ -682,34 +634,34 @@
   <cellStyleXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="44" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="164" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="165" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
   <cellXfs count="46">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="10" fontId="0" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="167" fontId="0" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="167" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="10" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="165" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="167" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="168" fontId="0" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="10" fontId="2" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="164" fontId="1" fillId="0" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="166" fontId="1" fillId="0" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="10" fontId="1" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="164" fontId="1" fillId="0" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1"/>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="166" fontId="1" fillId="0" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1"/>
     <xf numFmtId="10" fontId="1" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1"/>
-    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1"/>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="168" fontId="0" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="167" fontId="0" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1"/>
     <xf numFmtId="10" fontId="0" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1"/>
     <xf numFmtId="10" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="166" fontId="1" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="165" fontId="1" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="168" fontId="1" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="167" fontId="1" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
@@ -732,18 +684,18 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="166" fontId="1" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="168" fontId="1" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1"/>
     <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="165" fontId="1" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1"/>
-    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" xfId="3" applyFont="1"/>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="167" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="167" fontId="1" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="3" applyFont="1"/>
+    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="169" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="17" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="165" fontId="2" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="167" fontId="2" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1"/>
   </cellXfs>
   <cellStyles count="4">
     <cellStyle name="Comma" xfId="3" builtinId="3"/>
@@ -1027,186 +979,55 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2AB11DA5-57F8-4691-A562-35D1BBAF2472}">
-  <dimension ref="B2:E27"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <dimension ref="B2:B12"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="2" max="2" width="108.85546875" customWidth="1"/>
-    <col min="3" max="3" width="20.42578125" customWidth="1"/>
-    <col min="5" max="5" width="18.5703125" customWidth="1"/>
+    <col min="2" max="2" width="108.828125" customWidth="1"/>
+    <col min="3" max="3" width="20.4453125" customWidth="1"/>
+    <col min="5" max="5" width="18.5625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="2" spans="2:2" x14ac:dyDescent="0.2">
       <c r="B2" s="1" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="3" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="3" spans="2:2" x14ac:dyDescent="0.2">
       <c r="B3" s="6" t="s">
         <v>54</v>
       </c>
     </row>
-    <row r="4" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="4" spans="2:2" x14ac:dyDescent="0.2">
       <c r="B4" s="6" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="6" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="6" spans="2:2" x14ac:dyDescent="0.2">
       <c r="B6" s="6" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="8" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="8" spans="2:2" x14ac:dyDescent="0.2">
       <c r="B8" s="6" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="9" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="9" spans="2:2" x14ac:dyDescent="0.2">
       <c r="B9" s="6"/>
     </row>
-    <row r="10" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="10" spans="2:2" x14ac:dyDescent="0.2">
       <c r="B10" s="6" t="s">
         <v>34</v>
       </c>
     </row>
-    <row r="11" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="11" spans="2:2" x14ac:dyDescent="0.2">
       <c r="B11" s="6" t="s">
         <v>60</v>
       </c>
     </row>
-    <row r="12" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="12" spans="2:2" x14ac:dyDescent="0.2">
       <c r="B12" s="6" t="s">
         <v>61</v>
-      </c>
-    </row>
-    <row r="16" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="B16" s="1" t="s">
-        <v>136</v>
-      </c>
-      <c r="C16" s="1" t="s">
-        <v>137</v>
-      </c>
-      <c r="D16" s="1" t="s">
-        <v>138</v>
-      </c>
-      <c r="E16" s="1" t="s">
-        <v>151</v>
-      </c>
-    </row>
-    <row r="17" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="B17" t="s">
-        <v>108</v>
-      </c>
-      <c r="C17" t="s">
-        <v>115</v>
-      </c>
-      <c r="D17" t="s">
-        <v>135</v>
-      </c>
-      <c r="E17">
-        <v>2023</v>
-      </c>
-    </row>
-    <row r="18" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="B18" t="s">
-        <v>109</v>
-      </c>
-      <c r="C18" t="s">
-        <v>116</v>
-      </c>
-      <c r="D18" t="s">
-        <v>139</v>
-      </c>
-      <c r="E18">
-        <v>2023</v>
-      </c>
-    </row>
-    <row r="19" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="B19" t="s">
-        <v>110</v>
-      </c>
-      <c r="C19" t="s">
-        <v>115</v>
-      </c>
-      <c r="D19" t="s">
-        <v>135</v>
-      </c>
-    </row>
-    <row r="20" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="B20" t="s">
-        <v>111</v>
-      </c>
-      <c r="C20" t="s">
-        <v>115</v>
-      </c>
-      <c r="D20" t="s">
-        <v>135</v>
-      </c>
-    </row>
-    <row r="21" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="B21" t="s">
-        <v>112</v>
-      </c>
-      <c r="C21" t="s">
-        <v>116</v>
-      </c>
-      <c r="D21" t="s">
-        <v>139</v>
-      </c>
-    </row>
-    <row r="22" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="B22" t="s">
-        <v>113</v>
-      </c>
-      <c r="C22" t="s">
-        <v>115</v>
-      </c>
-      <c r="D22" t="s">
-        <v>135</v>
-      </c>
-    </row>
-    <row r="23" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="B23" t="s">
-        <v>114</v>
-      </c>
-      <c r="C23" s="44" t="s">
-        <v>117</v>
-      </c>
-      <c r="D23" t="s">
-        <v>140</v>
-      </c>
-      <c r="E23">
-        <v>2023</v>
-      </c>
-    </row>
-    <row r="25" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="B25" s="1"/>
-    </row>
-    <row r="26" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="B26" t="s">
-        <v>145</v>
-      </c>
-      <c r="C26" t="s">
-        <v>144</v>
-      </c>
-      <c r="D26" t="s">
-        <v>146</v>
-      </c>
-      <c r="E26">
-        <v>2022</v>
-      </c>
-    </row>
-    <row r="27" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="B27" t="s">
-        <v>99</v>
-      </c>
-      <c r="C27" t="s">
-        <v>143</v>
-      </c>
-      <c r="D27" t="s">
-        <v>147</v>
-      </c>
-      <c r="E27">
-        <v>2023</v>
       </c>
     </row>
   </sheetData>
@@ -1218,14 +1039,14 @@
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{045330D2-0890-4532-8ABA-CDB206A2E066}">
   <dimension ref="B1:P55"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="2" max="2" width="56.5703125" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="18.5703125" customWidth="1"/>
-    <col min="16" max="16" width="11.85546875" customWidth="1"/>
+    <col min="2" max="2" width="56.6328125" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="18.5625" customWidth="1"/>
+    <col min="16" max="16" width="11.8359375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:16" x14ac:dyDescent="0.25">
+    <row r="1" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C1" s="35">
         <v>2014</v>
       </c>
@@ -1264,7 +1085,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="2" spans="2:16" x14ac:dyDescent="0.25">
+    <row r="2" spans="2:16" x14ac:dyDescent="0.2">
       <c r="B2" s="24" t="s">
         <v>43</v>
       </c>
@@ -1301,7 +1122,7 @@
       <c r="N2" s="26"/>
       <c r="O2" s="26"/>
     </row>
-    <row r="3" spans="2:16" x14ac:dyDescent="0.25">
+    <row r="3" spans="2:16" x14ac:dyDescent="0.2">
       <c r="B3" s="24" t="s">
         <v>44</v>
       </c>
@@ -1335,7 +1156,7 @@
       <c r="N3" s="27"/>
       <c r="O3" s="27"/>
     </row>
-    <row r="4" spans="2:16" x14ac:dyDescent="0.25">
+    <row r="4" spans="2:16" x14ac:dyDescent="0.2">
       <c r="B4" s="24" t="s">
         <v>45</v>
       </c>
@@ -1369,7 +1190,7 @@
       <c r="N4" s="27"/>
       <c r="O4" s="27"/>
     </row>
-    <row r="5" spans="2:16" x14ac:dyDescent="0.25">
+    <row r="5" spans="2:16" x14ac:dyDescent="0.2">
       <c r="B5" s="24" t="s">
         <v>46</v>
       </c>
@@ -1414,7 +1235,7 @@
       </c>
       <c r="O5" s="27"/>
     </row>
-    <row r="6" spans="2:16" x14ac:dyDescent="0.25">
+    <row r="6" spans="2:16" x14ac:dyDescent="0.2">
       <c r="B6" s="24" t="s">
         <v>47</v>
       </c>
@@ -1459,13 +1280,13 @@
         <v>9.4999999999999793E-2</v>
       </c>
     </row>
-    <row r="7" spans="2:16" x14ac:dyDescent="0.25">
+    <row r="7" spans="2:16" x14ac:dyDescent="0.2">
       <c r="L7" s="26"/>
     </row>
-    <row r="8" spans="2:16" x14ac:dyDescent="0.25">
+    <row r="8" spans="2:16" x14ac:dyDescent="0.2">
       <c r="L8" s="26"/>
     </row>
-    <row r="9" spans="2:16" x14ac:dyDescent="0.25">
+    <row r="9" spans="2:16" x14ac:dyDescent="0.2">
       <c r="B9" s="29" t="s">
         <v>48</v>
       </c>
@@ -1498,9 +1319,9 @@
       <c r="M9" s="31"/>
       <c r="N9" s="31"/>
     </row>
-    <row r="10" spans="2:16" x14ac:dyDescent="0.25">
+    <row r="10" spans="2:16" x14ac:dyDescent="0.2">
       <c r="B10" s="29" t="s">
-        <v>118</v>
+        <v>111</v>
       </c>
       <c r="D10" s="30">
         <v>-13.55</v>
@@ -1528,9 +1349,9 @@
       <c r="M10" s="31"/>
       <c r="N10" s="31"/>
     </row>
-    <row r="11" spans="2:16" x14ac:dyDescent="0.25">
+    <row r="11" spans="2:16" x14ac:dyDescent="0.2">
       <c r="B11" s="29" t="s">
-        <v>119</v>
+        <v>112</v>
       </c>
       <c r="D11">
         <v>-13.86</v>
@@ -1558,7 +1379,7 @@
       <c r="M11" s="31"/>
       <c r="N11" s="31"/>
     </row>
-    <row r="12" spans="2:16" x14ac:dyDescent="0.25">
+    <row r="12" spans="2:16" x14ac:dyDescent="0.2">
       <c r="B12" s="29" t="s">
         <v>46</v>
       </c>
@@ -1601,7 +1422,7 @@
         <v>2016</v>
       </c>
     </row>
-    <row r="13" spans="2:16" x14ac:dyDescent="0.25">
+    <row r="13" spans="2:16" x14ac:dyDescent="0.2">
       <c r="B13" s="29" t="s">
         <v>47</v>
       </c>
@@ -1644,15 +1465,15 @@
         <v>2016</v>
       </c>
     </row>
-    <row r="14" spans="2:16" x14ac:dyDescent="0.25">
+    <row r="14" spans="2:16" x14ac:dyDescent="0.2">
       <c r="L14" s="26"/>
     </row>
-    <row r="15" spans="2:16" x14ac:dyDescent="0.25">
+    <row r="15" spans="2:16" x14ac:dyDescent="0.2">
       <c r="L15" s="26"/>
     </row>
-    <row r="16" spans="2:16" x14ac:dyDescent="0.25">
+    <row r="16" spans="2:16" x14ac:dyDescent="0.2">
       <c r="B16" s="34" t="s">
-        <v>124</v>
+        <v>117</v>
       </c>
       <c r="C16" s="31"/>
       <c r="D16" s="31"/>
@@ -1675,9 +1496,9 @@
       <c r="O16" s="31"/>
       <c r="P16" s="31"/>
     </row>
-    <row r="17" spans="2:16" x14ac:dyDescent="0.25">
+    <row r="17" spans="2:16" x14ac:dyDescent="0.2">
       <c r="B17" s="29" t="s">
-        <v>120</v>
+        <v>113</v>
       </c>
       <c r="C17" s="31"/>
       <c r="D17" s="31"/>
@@ -1700,9 +1521,9 @@
       <c r="O17" s="31"/>
       <c r="P17" s="31"/>
     </row>
-    <row r="18" spans="2:16" x14ac:dyDescent="0.25">
+    <row r="18" spans="2:16" x14ac:dyDescent="0.2">
       <c r="B18" s="29" t="s">
-        <v>121</v>
+        <v>114</v>
       </c>
       <c r="C18" s="31"/>
       <c r="D18" s="31"/>
@@ -1725,7 +1546,7 @@
       <c r="O18" s="31"/>
       <c r="P18" s="31"/>
     </row>
-    <row r="19" spans="2:16" x14ac:dyDescent="0.25">
+    <row r="19" spans="2:16" x14ac:dyDescent="0.2">
       <c r="B19" s="29" t="s">
         <v>46</v>
       </c>
@@ -1758,7 +1579,7 @@
         <v>2019</v>
       </c>
     </row>
-    <row r="20" spans="2:16" x14ac:dyDescent="0.25">
+    <row r="20" spans="2:16" x14ac:dyDescent="0.2">
       <c r="B20" s="29" t="s">
         <v>47</v>
       </c>
@@ -1784,13 +1605,13 @@
         <v>2019</v>
       </c>
     </row>
-    <row r="21" spans="2:16" x14ac:dyDescent="0.25">
+    <row r="21" spans="2:16" x14ac:dyDescent="0.2">
       <c r="L21" s="26"/>
     </row>
-    <row r="22" spans="2:16" x14ac:dyDescent="0.25">
+    <row r="22" spans="2:16" x14ac:dyDescent="0.2">
       <c r="L22" s="26"/>
     </row>
-    <row r="23" spans="2:16" x14ac:dyDescent="0.25">
+    <row r="23" spans="2:16" x14ac:dyDescent="0.2">
       <c r="B23" s="24" t="s">
         <v>64</v>
       </c>
@@ -1820,9 +1641,9 @@
         <v>8.2528571428571436</v>
       </c>
     </row>
-    <row r="24" spans="2:16" x14ac:dyDescent="0.25">
+    <row r="24" spans="2:16" x14ac:dyDescent="0.2">
       <c r="B24" s="29" t="s">
-        <v>122</v>
+        <v>115</v>
       </c>
       <c r="D24">
         <v>-6.57</v>
@@ -1847,9 +1668,9 @@
       </c>
       <c r="L24" s="26"/>
     </row>
-    <row r="25" spans="2:16" x14ac:dyDescent="0.25">
+    <row r="25" spans="2:16" x14ac:dyDescent="0.2">
       <c r="B25" s="29" t="s">
-        <v>123</v>
+        <v>116</v>
       </c>
       <c r="D25">
         <v>-6.85</v>
@@ -1874,7 +1695,7 @@
       </c>
       <c r="L25" s="26"/>
     </row>
-    <row r="26" spans="2:16" x14ac:dyDescent="0.25">
+    <row r="26" spans="2:16" x14ac:dyDescent="0.2">
       <c r="B26" s="24" t="s">
         <v>46</v>
       </c>
@@ -1912,7 +1733,7 @@
         <v>0.72428571428571331</v>
       </c>
     </row>
-    <row r="27" spans="2:16" x14ac:dyDescent="0.25">
+    <row r="27" spans="2:16" x14ac:dyDescent="0.2">
       <c r="B27" s="24" t="s">
         <v>47</v>
       </c>
@@ -1950,7 +1771,7 @@
         <v>-0.35000000000000003</v>
       </c>
     </row>
-    <row r="30" spans="2:16" x14ac:dyDescent="0.25">
+    <row r="30" spans="2:16" x14ac:dyDescent="0.2">
       <c r="B30" s="24" t="s">
         <v>71</v>
       </c>
@@ -1980,7 +1801,7 @@
         <v>7.055714285714286</v>
       </c>
     </row>
-    <row r="31" spans="2:16" x14ac:dyDescent="0.25">
+    <row r="31" spans="2:16" x14ac:dyDescent="0.2">
       <c r="B31" s="29" t="s">
         <v>50</v>
       </c>
@@ -2006,7 +1827,7 @@
         <v>-2.2200000000000002</v>
       </c>
     </row>
-    <row r="32" spans="2:16" x14ac:dyDescent="0.25">
+    <row r="32" spans="2:16" x14ac:dyDescent="0.2">
       <c r="B32" s="29" t="s">
         <v>49</v>
       </c>
@@ -2032,7 +1853,7 @@
         <v>-2.54</v>
       </c>
     </row>
-    <row r="33" spans="2:16" x14ac:dyDescent="0.25">
+    <row r="33" spans="2:16" x14ac:dyDescent="0.2">
       <c r="B33" s="24" t="s">
         <v>46</v>
       </c>
@@ -2069,7 +1890,7 @@
         <v>0.9242857142857146</v>
       </c>
     </row>
-    <row r="34" spans="2:16" x14ac:dyDescent="0.25">
+    <row r="34" spans="2:16" x14ac:dyDescent="0.2">
       <c r="B34" s="24" t="s">
         <v>47</v>
       </c>
@@ -2107,15 +1928,15 @@
         <v>-0.54000000000000048</v>
       </c>
     </row>
-    <row r="35" spans="2:16" x14ac:dyDescent="0.25">
+    <row r="35" spans="2:16" x14ac:dyDescent="0.2">
       <c r="N35" s="37"/>
       <c r="O35" s="37"/>
     </row>
-    <row r="36" spans="2:16" x14ac:dyDescent="0.25">
+    <row r="36" spans="2:16" x14ac:dyDescent="0.2">
       <c r="N36" s="37"/>
       <c r="O36" s="37"/>
     </row>
-    <row r="37" spans="2:16" x14ac:dyDescent="0.25">
+    <row r="37" spans="2:16" x14ac:dyDescent="0.2">
       <c r="B37" s="24" t="s">
         <v>76</v>
       </c>
@@ -2143,7 +1964,7 @@
       <c r="N37" s="37"/>
       <c r="O37" s="37"/>
     </row>
-    <row r="38" spans="2:16" x14ac:dyDescent="0.25">
+    <row r="38" spans="2:16" x14ac:dyDescent="0.2">
       <c r="B38" s="29" t="s">
         <v>50</v>
       </c>
@@ -2171,7 +1992,7 @@
       <c r="N38" s="37"/>
       <c r="O38" s="37"/>
     </row>
-    <row r="39" spans="2:16" x14ac:dyDescent="0.25">
+    <row r="39" spans="2:16" x14ac:dyDescent="0.2">
       <c r="B39" s="29" t="s">
         <v>49</v>
       </c>
@@ -2199,7 +2020,7 @@
       <c r="N39" s="37"/>
       <c r="O39" s="37"/>
     </row>
-    <row r="40" spans="2:16" x14ac:dyDescent="0.25">
+    <row r="40" spans="2:16" x14ac:dyDescent="0.2">
       <c r="B40" s="24" t="s">
         <v>46</v>
       </c>
@@ -2237,7 +2058,7 @@
       </c>
       <c r="O40" s="37"/>
     </row>
-    <row r="41" spans="2:16" x14ac:dyDescent="0.25">
+    <row r="41" spans="2:16" x14ac:dyDescent="0.2">
       <c r="B41" s="24" t="s">
         <v>47</v>
       </c>
@@ -2274,7 +2095,7 @@
         <v>-0.49571428571428516</v>
       </c>
     </row>
-    <row r="44" spans="2:16" x14ac:dyDescent="0.25">
+    <row r="44" spans="2:16" x14ac:dyDescent="0.2">
       <c r="B44" s="24" t="s">
         <v>83</v>
       </c>
@@ -2300,7 +2121,7 @@
         <v>20.03</v>
       </c>
     </row>
-    <row r="45" spans="2:16" x14ac:dyDescent="0.25">
+    <row r="45" spans="2:16" x14ac:dyDescent="0.2">
       <c r="B45" s="24" t="s">
         <v>84</v>
       </c>
@@ -2326,7 +2147,7 @@
         <v>20.77</v>
       </c>
     </row>
-    <row r="46" spans="2:16" x14ac:dyDescent="0.25">
+    <row r="46" spans="2:16" x14ac:dyDescent="0.2">
       <c r="B46" s="24" t="s">
         <v>85</v>
       </c>
@@ -2352,7 +2173,7 @@
         <v>20.04</v>
       </c>
     </row>
-    <row r="47" spans="2:16" x14ac:dyDescent="0.25">
+    <row r="47" spans="2:16" x14ac:dyDescent="0.2">
       <c r="B47" s="24" t="s">
         <v>46</v>
       </c>
@@ -2393,7 +2214,7 @@
         <v>2016</v>
       </c>
     </row>
-    <row r="48" spans="2:16" x14ac:dyDescent="0.25">
+    <row r="48" spans="2:16" x14ac:dyDescent="0.2">
       <c r="B48" s="24" t="s">
         <v>47</v>
       </c>
@@ -2433,9 +2254,9 @@
         <v>2016</v>
       </c>
     </row>
-    <row r="51" spans="2:14" x14ac:dyDescent="0.25">
+    <row r="51" spans="2:14" x14ac:dyDescent="0.2">
       <c r="B51" s="24" t="s">
-        <v>148</v>
+        <v>132</v>
       </c>
       <c r="D51">
         <v>3.83</v>
@@ -2462,9 +2283,9 @@
         <v>-17.87</v>
       </c>
     </row>
-    <row r="52" spans="2:14" x14ac:dyDescent="0.25">
+    <row r="52" spans="2:14" x14ac:dyDescent="0.2">
       <c r="B52" s="24" t="s">
-        <v>149</v>
+        <v>133</v>
       </c>
       <c r="D52">
         <v>4.54</v>
@@ -2491,12 +2312,12 @@
         <v>-17.34</v>
       </c>
     </row>
-    <row r="53" spans="2:14" x14ac:dyDescent="0.25">
+    <row r="53" spans="2:14" x14ac:dyDescent="0.2">
       <c r="B53" s="24" t="s">
-        <v>150</v>
-      </c>
-    </row>
-    <row r="54" spans="2:14" x14ac:dyDescent="0.25">
+        <v>134</v>
+      </c>
+    </row>
+    <row r="54" spans="2:14" x14ac:dyDescent="0.2">
       <c r="B54" s="24" t="s">
         <v>46</v>
       </c>
@@ -2537,7 +2358,7 @@
         <v>0.68375000000000052</v>
       </c>
     </row>
-    <row r="55" spans="2:14" x14ac:dyDescent="0.25">
+    <row r="55" spans="2:14" x14ac:dyDescent="0.2">
       <c r="B55" s="24" t="s">
         <v>47</v>
       </c>
@@ -2551,9 +2372,9 @@
 <file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1DB4ADDA-011E-42C7-847A-CF64D6C09BA3}">
   <dimension ref="B1:D9"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <sheetData>
-    <row r="1" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="1" spans="2:4" x14ac:dyDescent="0.2">
       <c r="C1" t="s">
         <v>94</v>
       </c>
@@ -2561,7 +2382,7 @@
         <v>95</v>
       </c>
     </row>
-    <row r="2" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="2" spans="2:4" x14ac:dyDescent="0.2">
       <c r="B2" s="42">
         <v>41730</v>
       </c>
@@ -2572,7 +2393,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="3" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="3" spans="2:4" x14ac:dyDescent="0.2">
       <c r="B3" s="42">
         <v>41760</v>
       </c>
@@ -2583,7 +2404,7 @@
         <v>37.5</v>
       </c>
     </row>
-    <row r="4" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="4" spans="2:4" x14ac:dyDescent="0.2">
       <c r="B4">
         <v>2016</v>
       </c>
@@ -2594,7 +2415,7 @@
         <v>37.5</v>
       </c>
     </row>
-    <row r="5" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="5" spans="2:4" x14ac:dyDescent="0.2">
       <c r="B5">
         <v>2017</v>
       </c>
@@ -2605,7 +2426,7 @@
         <v>37.5</v>
       </c>
     </row>
-    <row r="6" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="6" spans="2:4" x14ac:dyDescent="0.2">
       <c r="B6">
         <v>2018</v>
       </c>
@@ -2616,7 +2437,7 @@
         <v>37.5</v>
       </c>
     </row>
-    <row r="7" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="7" spans="2:4" x14ac:dyDescent="0.2">
       <c r="B7">
         <v>2019</v>
       </c>
@@ -2627,7 +2448,7 @@
         <v>37.5</v>
       </c>
     </row>
-    <row r="8" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="8" spans="2:4" x14ac:dyDescent="0.2">
       <c r="B8">
         <v>2020</v>
       </c>
@@ -2638,7 +2459,7 @@
         <v>37.5</v>
       </c>
     </row>
-    <row r="9" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="9" spans="2:4" x14ac:dyDescent="0.2">
       <c r="B9">
         <v>2021</v>
       </c>
@@ -2657,18 +2478,18 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A2:R42"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="36.42578125" customWidth="1"/>
-    <col min="2" max="9" width="17.7109375" customWidth="1"/>
-    <col min="10" max="10" width="14.140625" customWidth="1"/>
-    <col min="11" max="11" width="13.28515625" customWidth="1"/>
-    <col min="12" max="12" width="91.85546875" customWidth="1"/>
-    <col min="16" max="16" width="13.7109375" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="9.85546875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="36.453125" customWidth="1"/>
+    <col min="2" max="9" width="17.75390625" customWidth="1"/>
+    <col min="10" max="10" width="14.125" customWidth="1"/>
+    <col min="11" max="11" width="13.31640625" customWidth="1"/>
+    <col min="12" max="12" width="91.87890625" customWidth="1"/>
+    <col min="16" max="16" width="13.71875" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="9.81640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A2" s="8" t="s">
         <v>6</v>
       </c>
@@ -2685,7 +2506,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="3" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
         <v>19</v>
       </c>
@@ -2693,7 +2514,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="4" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:12" x14ac:dyDescent="0.2">
       <c r="B4" s="1">
         <v>2014</v>
       </c>
@@ -2725,7 +2546,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="5" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
         <v>12</v>
       </c>
@@ -2758,7 +2579,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="6" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
         <v>11</v>
       </c>
@@ -2790,7 +2611,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="7" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
         <v>13</v>
       </c>
@@ -2826,7 +2647,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="8" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
         <v>16</v>
       </c>
@@ -2864,7 +2685,7 @@
       </c>
       <c r="J8" s="5"/>
     </row>
-    <row r="9" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:12" x14ac:dyDescent="0.2">
       <c r="B9" s="20"/>
       <c r="C9" s="20"/>
       <c r="D9" s="20"/>
@@ -2878,7 +2699,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="10" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A10" t="s">
         <v>7</v>
       </c>
@@ -2911,7 +2732,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="11" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A11" t="s">
         <v>9</v>
       </c>
@@ -2941,7 +2762,7 @@
       </c>
       <c r="J11" s="5"/>
     </row>
-    <row r="12" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A12" t="s">
         <v>10</v>
       </c>
@@ -2985,7 +2806,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="13" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A13" t="s">
         <v>28</v>
       </c>
@@ -3029,7 +2850,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="14" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A14" t="s">
         <v>90</v>
       </c>
@@ -3070,7 +2891,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="15" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:12" x14ac:dyDescent="0.2">
       <c r="B15" s="16"/>
       <c r="C15" s="16"/>
       <c r="D15" s="16"/>
@@ -3081,7 +2902,7 @@
       <c r="I15" s="16"/>
       <c r="J15" s="5"/>
     </row>
-    <row r="16" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A16" t="s">
         <v>8</v>
       </c>
@@ -3111,10 +2932,10 @@
       </c>
       <c r="J16" s="5"/>
       <c r="L16" t="s">
-        <v>134</v>
-      </c>
-    </row>
-    <row r="17" spans="1:18" x14ac:dyDescent="0.25">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="17" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A17" t="s">
         <v>21</v>
       </c>
@@ -3155,7 +2976,7 @@
         <v>2.0161757276515154E-4</v>
       </c>
     </row>
-    <row r="18" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A18" t="s">
         <v>59</v>
       </c>
@@ -3188,10 +3009,10 @@
       </c>
       <c r="J18" s="4"/>
       <c r="L18" t="s">
-        <v>115</v>
-      </c>
-    </row>
-    <row r="19" spans="1:18" x14ac:dyDescent="0.25">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="19" spans="1:18" x14ac:dyDescent="0.2">
       <c r="B19" s="15"/>
       <c r="C19" s="15"/>
       <c r="D19" s="16"/>
@@ -3202,7 +3023,7 @@
       <c r="I19" s="16"/>
       <c r="J19" s="5"/>
     </row>
-    <row r="20" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A20" t="s">
         <v>0</v>
       </c>
@@ -3232,7 +3053,7 @@
       </c>
       <c r="J20" s="5"/>
     </row>
-    <row r="21" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A21" t="s">
         <v>1</v>
       </c>
@@ -3273,7 +3094,7 @@
         <v>3.1031841487049795E-4</v>
       </c>
     </row>
-    <row r="22" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:18" x14ac:dyDescent="0.2">
       <c r="B22" s="20"/>
       <c r="C22" s="20"/>
       <c r="D22" s="20"/>
@@ -3284,7 +3105,7 @@
       <c r="I22" s="20"/>
       <c r="J22" s="5"/>
     </row>
-    <row r="23" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A23" t="s">
         <v>58</v>
       </c>
@@ -3310,10 +3131,10 @@
       <c r="I23" s="20"/>
       <c r="J23" s="5"/>
     </row>
-    <row r="24" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:18" x14ac:dyDescent="0.2">
       <c r="J24" s="19"/>
     </row>
-    <row r="25" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A25" t="s">
         <v>41</v>
       </c>
@@ -3322,7 +3143,7 @@
         <v>5.3014254570528723E-3</v>
       </c>
       <c r="C25" t="s">
-        <v>125</v>
+        <v>118</v>
       </c>
       <c r="D25" s="10"/>
       <c r="E25" s="10"/>
@@ -3334,7 +3155,7 @@
       <c r="L25" s="6"/>
       <c r="P25" s="5"/>
     </row>
-    <row r="26" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A26" t="s">
         <v>42</v>
       </c>
@@ -3343,12 +3164,12 @@
         <v>5.0375000000000038E-3</v>
       </c>
       <c r="C26" t="s">
-        <v>125</v>
+        <v>118</v>
       </c>
       <c r="L26" s="6"/>
       <c r="P26" s="39"/>
     </row>
-    <row r="27" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A27" t="s">
         <v>27</v>
       </c>
@@ -3358,12 +3179,12 @@
       </c>
       <c r="L27" s="6"/>
     </row>
-    <row r="28" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:18" x14ac:dyDescent="0.2">
       <c r="E28" s="20"/>
       <c r="K28" s="4"/>
       <c r="L28" s="6"/>
     </row>
-    <row r="29" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A29" s="1" t="s">
         <v>3</v>
       </c>
@@ -3374,7 +3195,7 @@
       <c r="K29" s="4"/>
       <c r="L29" s="6"/>
     </row>
-    <row r="30" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A30" s="1" t="s">
         <v>77</v>
       </c>
@@ -3385,11 +3206,11 @@
       <c r="K30" s="4"/>
       <c r="L30" s="6"/>
     </row>
-    <row r="31" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:18" x14ac:dyDescent="0.2">
       <c r="B31" s="5"/>
       <c r="K31" s="4"/>
     </row>
-    <row r="32" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:18" x14ac:dyDescent="0.2">
       <c r="B32" s="5"/>
       <c r="C32" s="10"/>
       <c r="D32" s="10"/>
@@ -3403,7 +3224,7 @@
       <c r="P32" s="2"/>
       <c r="R32" s="40"/>
     </row>
-    <row r="33" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:11" x14ac:dyDescent="0.2">
       <c r="B33" s="10"/>
       <c r="C33" s="10"/>
       <c r="D33" s="10"/>
@@ -3415,7 +3236,7 @@
       <c r="J33" s="3"/>
       <c r="K33" s="4"/>
     </row>
-    <row r="34" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A34" s="1"/>
       <c r="B34" s="10"/>
       <c r="C34" s="10"/>
@@ -3428,7 +3249,7 @@
       <c r="J34" s="3"/>
       <c r="K34" s="4"/>
     </row>
-    <row r="35" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A35" s="1"/>
       <c r="B35" s="21"/>
       <c r="C35" s="10"/>
@@ -3441,7 +3262,7 @@
       <c r="J35" s="3"/>
       <c r="K35" s="4"/>
     </row>
-    <row r="36" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A36" s="1"/>
       <c r="B36" s="21"/>
       <c r="C36" s="10"/>
@@ -3454,7 +3275,7 @@
       <c r="J36" s="3"/>
       <c r="K36" s="4"/>
     </row>
-    <row r="37" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A37" s="1"/>
       <c r="B37" s="1"/>
       <c r="C37" s="10"/>
@@ -3467,7 +3288,7 @@
       <c r="J37" s="3"/>
       <c r="K37" s="4"/>
     </row>
-    <row r="38" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A38" s="1"/>
       <c r="B38" s="1"/>
       <c r="C38" s="10"/>
@@ -3480,7 +3301,7 @@
       <c r="J38" s="3"/>
       <c r="K38" s="4"/>
     </row>
-    <row r="39" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A39" s="1"/>
       <c r="B39" s="1"/>
       <c r="C39" s="10"/>
@@ -3493,7 +3314,7 @@
       <c r="J39" s="3"/>
       <c r="K39" s="4"/>
     </row>
-    <row r="40" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A40" s="1"/>
       <c r="B40" s="1"/>
       <c r="C40" s="10"/>
@@ -3506,7 +3327,7 @@
       <c r="J40" s="3"/>
       <c r="K40" s="4"/>
     </row>
-    <row r="41" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A41" s="1"/>
       <c r="B41" s="1"/>
       <c r="C41" s="10"/>
@@ -3519,7 +3340,7 @@
       <c r="J41" s="3"/>
       <c r="K41" s="4"/>
     </row>
-    <row r="42" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A42" s="1"/>
       <c r="B42" s="1"/>
       <c r="C42" s="10"/>
@@ -3541,16 +3362,16 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{85662431-B8A3-40F8-9BF4-EC97DECEFC14}">
   <dimension ref="A2:M31"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="38.5703125" customWidth="1"/>
-    <col min="2" max="10" width="17.7109375" customWidth="1"/>
-    <col min="11" max="11" width="15" customWidth="1"/>
-    <col min="12" max="12" width="13.28515625" customWidth="1"/>
-    <col min="13" max="13" width="104.85546875" customWidth="1"/>
+    <col min="1" max="1" width="38.60546875" customWidth="1"/>
+    <col min="2" max="10" width="17.75390625" customWidth="1"/>
+    <col min="11" max="11" width="14.9296875" customWidth="1"/>
+    <col min="12" max="12" width="13.31640625" customWidth="1"/>
+    <col min="13" max="13" width="104.79296875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A2" s="8" t="s">
         <v>98</v>
       </c>
@@ -3568,7 +3389,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="3" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
         <v>32</v>
       </c>
@@ -3576,7 +3397,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="4" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:13" x14ac:dyDescent="0.2">
       <c r="B4" s="1">
         <v>2016</v>
       </c>
@@ -3606,7 +3427,7 @@
       </c>
       <c r="M4" s="6"/>
     </row>
-    <row r="5" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
         <v>12</v>
       </c>
@@ -3638,7 +3459,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="6" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
         <v>11</v>
       </c>
@@ -3670,7 +3491,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="7" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
         <v>13</v>
       </c>
@@ -3706,7 +3527,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="8" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
         <v>16</v>
       </c>
@@ -3746,7 +3567,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="9" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:13" x14ac:dyDescent="0.2">
       <c r="B9" s="2"/>
       <c r="C9" s="2"/>
       <c r="D9" s="2"/>
@@ -3757,7 +3578,7 @@
       <c r="I9" s="2"/>
       <c r="M9" s="6"/>
     </row>
-    <row r="10" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A10" t="s">
         <v>7</v>
       </c>
@@ -3789,7 +3610,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="11" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A11" t="s">
         <v>9</v>
       </c>
@@ -3822,7 +3643,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="12" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A12" t="s">
         <v>10</v>
       </c>
@@ -3866,7 +3687,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="13" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A13" t="s">
         <v>35</v>
       </c>
@@ -3907,7 +3728,7 @@
         <v>3.2524956258138207E-3</v>
       </c>
     </row>
-    <row r="14" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:13" x14ac:dyDescent="0.2">
       <c r="B14" s="13"/>
       <c r="C14" s="13"/>
       <c r="D14" s="13"/>
@@ -3917,10 +3738,10 @@
       <c r="H14" s="13"/>
       <c r="I14" s="13"/>
       <c r="M14" t="s">
-        <v>126</v>
-      </c>
-    </row>
-    <row r="15" spans="1:13" x14ac:dyDescent="0.25">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="15" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A15" t="s">
         <v>8</v>
       </c>
@@ -3949,7 +3770,7 @@
         <v>16552</v>
       </c>
     </row>
-    <row r="16" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A16" t="s">
         <v>21</v>
       </c>
@@ -3990,10 +3811,10 @@
         <v>9.9519927879822669E-4</v>
       </c>
       <c r="M16" t="s">
-        <v>116</v>
-      </c>
-    </row>
-    <row r="17" spans="1:12" x14ac:dyDescent="0.25">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="17" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A17" t="s">
         <v>59</v>
       </c>
@@ -4024,7 +3845,7 @@
       </c>
       <c r="J17" s="5"/>
     </row>
-    <row r="18" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:12" x14ac:dyDescent="0.2">
       <c r="B18" s="13"/>
       <c r="C18" s="13"/>
       <c r="D18" s="13"/>
@@ -4034,7 +3855,7 @@
       <c r="H18" s="13"/>
       <c r="I18" s="13"/>
     </row>
-    <row r="19" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A19" t="s">
         <v>0</v>
       </c>
@@ -4061,7 +3882,7 @@
         <v>3687</v>
       </c>
     </row>
-    <row r="20" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A20" t="s">
         <v>1</v>
       </c>
@@ -4099,7 +3920,7 @@
         <v>5.3066791104811257E-4</v>
       </c>
     </row>
-    <row r="21" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:12" x14ac:dyDescent="0.2">
       <c r="B21" s="4"/>
       <c r="C21" s="4"/>
       <c r="D21" s="23"/>
@@ -4110,7 +3931,7 @@
       <c r="I21" s="23"/>
       <c r="J21" s="23"/>
     </row>
-    <row r="22" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:12" x14ac:dyDescent="0.2">
       <c r="B22" s="10"/>
       <c r="C22" s="10"/>
       <c r="D22" s="10"/>
@@ -4122,7 +3943,7 @@
       <c r="J22" s="3"/>
       <c r="K22" s="3"/>
     </row>
-    <row r="23" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A23" t="s">
         <v>41</v>
       </c>
@@ -4131,11 +3952,11 @@
         <v>4.875464258063707E-3</v>
       </c>
       <c r="C23" t="s">
-        <v>142</v>
+        <v>129</v>
       </c>
       <c r="L23" s="4"/>
     </row>
-    <row r="24" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A24" t="s">
         <v>42</v>
       </c>
@@ -4144,10 +3965,10 @@
         <v>4.1500000000000113E-3</v>
       </c>
       <c r="C24" t="s">
-        <v>127</v>
-      </c>
-    </row>
-    <row r="25" spans="1:12" x14ac:dyDescent="0.25">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="25" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A25" t="s">
         <v>27</v>
       </c>
@@ -4156,7 +3977,7 @@
         <v>-7.2546425806369573E-4</v>
       </c>
     </row>
-    <row r="27" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A27" s="1" t="s">
         <v>3</v>
       </c>
@@ -4165,7 +3986,7 @@
         <v>4.7452124142958419E-3</v>
       </c>
     </row>
-    <row r="28" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A28" s="1" t="s">
         <v>77</v>
       </c>
@@ -4174,7 +3995,7 @@
         <v>1.4927167884820213E-3</v>
       </c>
     </row>
-    <row r="31" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A31" s="1"/>
       <c r="B31" s="21"/>
     </row>
@@ -4187,16 +4008,16 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1C9A39DF-ECA7-4B8A-BED1-414B316C3BE0}">
   <dimension ref="A2:M31"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="39.5703125" customWidth="1"/>
-    <col min="2" max="10" width="17.7109375" customWidth="1"/>
-    <col min="11" max="11" width="18.85546875" customWidth="1"/>
-    <col min="12" max="12" width="13.28515625" customWidth="1"/>
-    <col min="13" max="13" width="91.85546875" customWidth="1"/>
+    <col min="1" max="1" width="39.546875" customWidth="1"/>
+    <col min="2" max="10" width="17.75390625" customWidth="1"/>
+    <col min="11" max="11" width="18.83203125" customWidth="1"/>
+    <col min="12" max="12" width="13.31640625" customWidth="1"/>
+    <col min="13" max="13" width="91.87890625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A2" s="8" t="s">
         <v>70</v>
       </c>
@@ -4214,7 +4035,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="3" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
         <v>74</v>
       </c>
@@ -4222,7 +4043,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="4" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:13" x14ac:dyDescent="0.2">
       <c r="B4" s="1">
         <v>2014</v>
       </c>
@@ -4257,7 +4078,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="5" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
         <v>12</v>
       </c>
@@ -4290,7 +4111,7 @@
       </c>
       <c r="K5" s="1"/>
     </row>
-    <row r="6" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
         <v>11</v>
       </c>
@@ -4322,10 +4143,10 @@
         <v>7292</v>
       </c>
       <c r="M6" t="s">
-        <v>128</v>
-      </c>
-    </row>
-    <row r="7" spans="1:13" x14ac:dyDescent="0.25">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="7" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
         <v>13</v>
       </c>
@@ -4361,7 +4182,7 @@
         <v>6.0750000000000005E-3</v>
       </c>
     </row>
-    <row r="8" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
         <v>16</v>
       </c>
@@ -4406,7 +4227,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="9" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:13" x14ac:dyDescent="0.2">
       <c r="B9" s="1"/>
       <c r="C9" s="1"/>
       <c r="D9" s="1"/>
@@ -4418,7 +4239,7 @@
       <c r="J9" s="1"/>
       <c r="K9" s="21"/>
     </row>
-    <row r="10" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A10" t="s">
         <v>7</v>
       </c>
@@ -4451,10 +4272,10 @@
       </c>
       <c r="K10" s="5"/>
       <c r="M10" t="s">
-        <v>129</v>
-      </c>
-    </row>
-    <row r="11" spans="1:13" x14ac:dyDescent="0.25">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="11" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A11" t="s">
         <v>9</v>
       </c>
@@ -4487,7 +4308,7 @@
       </c>
       <c r="K11" s="5"/>
     </row>
-    <row r="12" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A12" t="s">
         <v>10</v>
       </c>
@@ -4532,10 +4353,10 @@
         <v>0.16060970398346097</v>
       </c>
       <c r="M12" t="s">
-        <v>116</v>
-      </c>
-    </row>
-    <row r="13" spans="1:13" x14ac:dyDescent="0.25">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="13" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A13" t="s">
         <v>28</v>
       </c>
@@ -4580,7 +4401,7 @@
         <v>4.1509587896926227E-3</v>
       </c>
     </row>
-    <row r="14" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:13" x14ac:dyDescent="0.2">
       <c r="B14" s="9"/>
       <c r="C14" s="9"/>
       <c r="D14" s="9"/>
@@ -4592,7 +4413,7 @@
       <c r="J14" s="9"/>
       <c r="K14" s="5"/>
     </row>
-    <row r="15" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A15" t="s">
         <v>8</v>
       </c>
@@ -4625,7 +4446,7 @@
       </c>
       <c r="K15" s="5"/>
     </row>
-    <row r="16" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A16" t="s">
         <v>21</v>
       </c>
@@ -4670,7 +4491,7 @@
         <v>5.5636948289860329E-4</v>
       </c>
     </row>
-    <row r="17" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A17" t="s">
         <v>59</v>
       </c>
@@ -4706,7 +4527,7 @@
       </c>
       <c r="K17" s="5"/>
     </row>
-    <row r="18" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:13" x14ac:dyDescent="0.2">
       <c r="B18" s="9"/>
       <c r="C18" s="9"/>
       <c r="D18" s="9"/>
@@ -4718,7 +4539,7 @@
       <c r="J18" s="9"/>
       <c r="K18" s="5"/>
     </row>
-    <row r="19" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A19" t="s">
         <v>0</v>
       </c>
@@ -4749,7 +4570,7 @@
       </c>
       <c r="K19" s="5"/>
     </row>
-    <row r="20" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A20" t="s">
         <v>1</v>
       </c>
@@ -4792,11 +4613,11 @@
       </c>
       <c r="M20" s="6"/>
     </row>
-    <row r="21" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:13" x14ac:dyDescent="0.2">
       <c r="K21" s="3"/>
       <c r="M21" s="6"/>
     </row>
-    <row r="22" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:13" x14ac:dyDescent="0.2">
       <c r="B22" s="20"/>
       <c r="C22" s="20"/>
       <c r="D22" s="10"/>
@@ -4809,7 +4630,7 @@
       <c r="K22" s="3"/>
       <c r="M22" s="6"/>
     </row>
-    <row r="23" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A23" t="s">
         <v>41</v>
       </c>
@@ -4818,10 +4639,10 @@
         <v>1.0310465759840078E-2</v>
       </c>
       <c r="C23" t="s">
-        <v>141</v>
-      </c>
-    </row>
-    <row r="24" spans="1:13" x14ac:dyDescent="0.25">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="24" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A24" t="s">
         <v>42</v>
       </c>
@@ -4830,10 +4651,10 @@
         <v>9.2428571428571464E-3</v>
       </c>
       <c r="C24" t="s">
-        <v>130</v>
-      </c>
-    </row>
-    <row r="25" spans="1:13" x14ac:dyDescent="0.25">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="25" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A25" t="s">
         <v>27</v>
       </c>
@@ -4842,7 +4663,7 @@
         <v>-1.0676086169829312E-3</v>
       </c>
     </row>
-    <row r="27" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A27" s="1" t="s">
         <v>3</v>
       </c>
@@ -4851,17 +4672,17 @@
         <v>6.4386891566194041E-3</v>
       </c>
     </row>
-    <row r="28" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A28" s="1"/>
       <c r="B28" s="21"/>
     </row>
-    <row r="29" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:13" x14ac:dyDescent="0.2">
       <c r="B29" s="5"/>
     </row>
-    <row r="30" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A30" s="1"/>
     </row>
-    <row r="31" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A31" s="1"/>
       <c r="B31" s="21"/>
     </row>
@@ -4874,16 +4695,16 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CF4E9972-EF6D-435D-B893-B5209367B0F1}">
   <dimension ref="A2:L31"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="39.5703125" customWidth="1"/>
-    <col min="2" max="9" width="17.7109375" customWidth="1"/>
-    <col min="10" max="10" width="18.5703125" customWidth="1"/>
-    <col min="11" max="11" width="13.28515625" customWidth="1"/>
-    <col min="12" max="12" width="91.85546875" customWidth="1"/>
+    <col min="1" max="1" width="39.546875" customWidth="1"/>
+    <col min="2" max="9" width="17.75390625" customWidth="1"/>
+    <col min="10" max="10" width="18.5625" customWidth="1"/>
+    <col min="11" max="11" width="13.31640625" customWidth="1"/>
+    <col min="12" max="12" width="91.87890625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A2" s="8" t="s">
         <v>75</v>
       </c>
@@ -4900,7 +4721,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="3" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
         <v>19</v>
       </c>
@@ -4908,7 +4729,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="4" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:12" x14ac:dyDescent="0.2">
       <c r="B4" s="1">
         <v>2014</v>
       </c>
@@ -4937,7 +4758,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="5" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
         <v>12</v>
       </c>
@@ -4970,7 +4791,7 @@
         <v>97</v>
       </c>
     </row>
-    <row r="6" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
         <v>11</v>
       </c>
@@ -5002,7 +4823,7 @@
         <v>72</v>
       </c>
     </row>
-    <row r="7" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
         <v>13</v>
       </c>
@@ -5036,7 +4857,7 @@
         <v>5.8983606557377046E-3</v>
       </c>
     </row>
-    <row r="8" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
         <v>16</v>
       </c>
@@ -5074,10 +4895,10 @@
       </c>
       <c r="J8" s="21"/>
       <c r="L8" t="s">
-        <v>131</v>
-      </c>
-    </row>
-    <row r="9" spans="1:12" x14ac:dyDescent="0.25">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="9" spans="1:12" x14ac:dyDescent="0.2">
       <c r="B9" s="1"/>
       <c r="C9" s="1"/>
       <c r="D9" s="1"/>
@@ -5088,7 +4909,7 @@
       <c r="I9" s="1"/>
       <c r="J9" s="21"/>
     </row>
-    <row r="10" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A10" t="s">
         <v>7</v>
       </c>
@@ -5118,10 +4939,10 @@
       </c>
       <c r="J10" s="5"/>
       <c r="L10" t="s">
-        <v>115</v>
-      </c>
-    </row>
-    <row r="11" spans="1:12" x14ac:dyDescent="0.25">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="11" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A11" t="s">
         <v>9</v>
       </c>
@@ -5151,7 +4972,7 @@
       </c>
       <c r="J11" s="5"/>
     </row>
-    <row r="12" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A12" t="s">
         <v>10</v>
       </c>
@@ -5192,7 +5013,7 @@
         <v>0.12879362167170424</v>
       </c>
     </row>
-    <row r="13" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A13" t="s">
         <v>28</v>
       </c>
@@ -5233,7 +5054,7 @@
         <v>3.5018420436858299E-3</v>
       </c>
     </row>
-    <row r="14" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:12" x14ac:dyDescent="0.2">
       <c r="B14" s="9"/>
       <c r="C14" s="9"/>
       <c r="D14" s="9"/>
@@ -5244,7 +5065,7 @@
       <c r="I14" s="9"/>
       <c r="J14" s="5"/>
     </row>
-    <row r="15" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A15" t="s">
         <v>8</v>
       </c>
@@ -5274,7 +5095,7 @@
       </c>
       <c r="J15" s="5"/>
     </row>
-    <row r="16" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A16" t="s">
         <v>21</v>
       </c>
@@ -5315,7 +5136,7 @@
         <v>5.2706372061526281E-4</v>
       </c>
     </row>
-    <row r="17" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A17" t="s">
         <v>59</v>
       </c>
@@ -5348,7 +5169,7 @@
       </c>
       <c r="J17" s="5"/>
     </row>
-    <row r="18" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:12" x14ac:dyDescent="0.2">
       <c r="B18" s="9"/>
       <c r="C18" s="9"/>
       <c r="D18" s="9"/>
@@ -5359,7 +5180,7 @@
       <c r="I18" s="9"/>
       <c r="J18" s="5"/>
     </row>
-    <row r="19" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A19" t="s">
         <v>0</v>
       </c>
@@ -5389,7 +5210,7 @@
       </c>
       <c r="J19" s="5"/>
     </row>
-    <row r="20" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A20" t="s">
         <v>1</v>
       </c>
@@ -5431,11 +5252,11 @@
       </c>
       <c r="L20" s="6"/>
     </row>
-    <row r="21" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:12" x14ac:dyDescent="0.2">
       <c r="J21" s="3"/>
       <c r="L21" s="6"/>
     </row>
-    <row r="22" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:12" x14ac:dyDescent="0.2">
       <c r="B22" s="20"/>
       <c r="C22" s="20"/>
       <c r="D22" s="10"/>
@@ -5447,7 +5268,7 @@
       <c r="J22" s="3"/>
       <c r="L22" s="6"/>
     </row>
-    <row r="23" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A23" t="s">
         <v>41</v>
       </c>
@@ -5456,10 +5277,10 @@
         <v>9.6913226448098518E-3</v>
       </c>
       <c r="C23" t="s">
-        <v>130</v>
-      </c>
-    </row>
-    <row r="24" spans="1:12" x14ac:dyDescent="0.25">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="24" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A24" t="s">
         <v>42</v>
       </c>
@@ -5468,10 +5289,10 @@
         <v>8.7999999999999919E-3</v>
       </c>
       <c r="C24" t="s">
-        <v>130</v>
-      </c>
-    </row>
-    <row r="25" spans="1:12" x14ac:dyDescent="0.25">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="25" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A25" t="s">
         <v>27</v>
       </c>
@@ -5480,7 +5301,7 @@
         <v>-8.9132264480985997E-4</v>
       </c>
     </row>
-    <row r="27" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A27" s="1" t="s">
         <v>3</v>
       </c>
@@ -5489,17 +5310,17 @@
         <v>5.6086527039202212E-3</v>
       </c>
     </row>
-    <row r="28" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A28" s="1"/>
       <c r="B28" s="21"/>
     </row>
-    <row r="29" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:12" x14ac:dyDescent="0.2">
       <c r="B29" s="5"/>
     </row>
-    <row r="30" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A30" s="1"/>
     </row>
-    <row r="31" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A31" s="1"/>
       <c r="B31" s="21"/>
     </row>
@@ -5511,15 +5332,15 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3319A48F-C74C-4C2A-9714-F1A50A94B19B}">
   <dimension ref="A2:G34"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="32.28515625" customWidth="1"/>
-    <col min="2" max="5" width="17.7109375" customWidth="1"/>
-    <col min="6" max="6" width="13.28515625" customWidth="1"/>
-    <col min="7" max="7" width="91.85546875" customWidth="1"/>
+    <col min="2" max="5" width="17.75390625" customWidth="1"/>
+    <col min="6" max="6" width="13.31640625" customWidth="1"/>
+    <col min="7" max="7" width="91.87890625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A2" s="8" t="s">
         <v>23</v>
       </c>
@@ -5531,7 +5352,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
         <v>22</v>
       </c>
@@ -5539,7 +5360,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:7" x14ac:dyDescent="0.2">
       <c r="B4" s="1">
         <v>2019</v>
       </c>
@@ -5556,7 +5377,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
         <v>12</v>
       </c>
@@ -5572,7 +5393,7 @@
       <c r="E5" s="1"/>
       <c r="G5" s="6"/>
     </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
         <v>11</v>
       </c>
@@ -5586,10 +5407,10 @@
         <v>9212</v>
       </c>
       <c r="G6" t="s">
-        <v>131</v>
-      </c>
-    </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.25">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
         <v>13</v>
       </c>
@@ -5608,7 +5429,7 @@
       </c>
       <c r="G7" s="6"/>
     </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
         <v>16</v>
       </c>
@@ -5626,17 +5447,17 @@
       </c>
       <c r="E8" s="1"/>
       <c r="G8" t="s">
-        <v>115</v>
-      </c>
-    </row>
-    <row r="9" spans="1:7" x14ac:dyDescent="0.25">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7" x14ac:dyDescent="0.2">
       <c r="B9" s="1"/>
       <c r="C9" s="1"/>
       <c r="D9" s="1"/>
       <c r="E9" s="1"/>
       <c r="G9" s="6"/>
     </row>
-    <row r="10" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A10" t="s">
         <v>7</v>
       </c>
@@ -5650,7 +5471,7 @@
         <v>46407</v>
       </c>
     </row>
-    <row r="11" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A11" t="s">
         <v>9</v>
       </c>
@@ -5664,7 +5485,7 @@
         <v>5654</v>
       </c>
     </row>
-    <row r="12" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A12" t="s">
         <v>10</v>
       </c>
@@ -5685,7 +5506,7 @@
         <v>0.1237441643040095</v>
       </c>
     </row>
-    <row r="13" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A13" t="s">
         <v>35</v>
       </c>
@@ -5706,12 +5527,12 @@
         <v>2.2811352303993069E-3</v>
       </c>
     </row>
-    <row r="14" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:7" x14ac:dyDescent="0.2">
       <c r="B14" s="9"/>
       <c r="C14" s="9"/>
       <c r="D14" s="9"/>
     </row>
-    <row r="15" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A15" t="s">
         <v>8</v>
       </c>
@@ -5725,7 +5546,7 @@
         <v>1908</v>
       </c>
     </row>
-    <row r="16" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A16" t="s">
         <v>21</v>
       </c>
@@ -5746,7 +5567,7 @@
         <v>7.7499708559259143E-4</v>
       </c>
     </row>
-    <row r="17" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A17" t="s">
         <v>59</v>
       </c>
@@ -5761,12 +5582,12 @@
       </c>
       <c r="E17" s="5"/>
     </row>
-    <row r="18" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:7" x14ac:dyDescent="0.2">
       <c r="B18" s="9"/>
       <c r="C18" s="9"/>
       <c r="D18" s="9"/>
     </row>
-    <row r="19" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A19" t="s">
         <v>0</v>
       </c>
@@ -5780,7 +5601,7 @@
         <v>1108</v>
       </c>
     </row>
-    <row r="20" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A20" t="s">
         <v>1</v>
       </c>
@@ -5802,17 +5623,17 @@
       </c>
       <c r="G20" s="6"/>
     </row>
-    <row r="21" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:7" x14ac:dyDescent="0.2">
       <c r="E21" s="3"/>
       <c r="G21" s="6"/>
     </row>
-    <row r="22" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:7" x14ac:dyDescent="0.2">
       <c r="C22" s="3"/>
       <c r="D22" s="3"/>
       <c r="E22" s="3"/>
       <c r="G22" s="6"/>
     </row>
-    <row r="23" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A23" t="s">
         <v>40</v>
       </c>
@@ -5821,13 +5642,13 @@
         <v>5.5074726116786706E-3</v>
       </c>
       <c r="C23" s="45" t="s">
-        <v>133</v>
+        <v>126</v>
       </c>
       <c r="D23" s="3"/>
       <c r="E23" s="3"/>
       <c r="G23" s="6"/>
     </row>
-    <row r="24" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A24" t="s">
         <v>42</v>
       </c>
@@ -5836,11 +5657,11 @@
         <v>5.0499999999999903E-3</v>
       </c>
       <c r="C24" s="45" t="s">
-        <v>133</v>
+        <v>126</v>
       </c>
       <c r="G24" s="6"/>
     </row>
-    <row r="25" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A25" t="s">
         <v>27</v>
       </c>
@@ -5851,16 +5672,16 @@
       <c r="F25" s="4"/>
       <c r="G25" s="6"/>
     </row>
-    <row r="26" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:7" x14ac:dyDescent="0.2">
       <c r="F26" s="4"/>
       <c r="G26" s="6"/>
     </row>
-    <row r="27" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A27" s="1"/>
       <c r="B27" s="12"/>
       <c r="F27" s="4"/>
     </row>
-    <row r="28" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A28" s="1"/>
       <c r="B28" s="2"/>
       <c r="C28" s="3"/>
@@ -5868,7 +5689,7 @@
       <c r="E28" s="3"/>
       <c r="F28" s="4"/>
     </row>
-    <row r="29" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A29" s="1"/>
       <c r="B29" s="3"/>
       <c r="C29" s="3"/>
@@ -5876,7 +5697,7 @@
       <c r="E29" s="3"/>
       <c r="F29" s="4"/>
     </row>
-    <row r="30" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A30" s="1"/>
       <c r="B30" s="3"/>
       <c r="C30" s="3"/>
@@ -5884,14 +5705,14 @@
       <c r="E30" s="3"/>
       <c r="F30" s="4"/>
     </row>
-    <row r="31" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:7" x14ac:dyDescent="0.2">
       <c r="B31" s="3"/>
       <c r="C31" s="3"/>
       <c r="D31" s="3"/>
       <c r="E31" s="3"/>
       <c r="F31" s="4"/>
     </row>
-    <row r="32" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A32" s="1"/>
       <c r="B32" s="3"/>
       <c r="C32" s="3"/>
@@ -5899,7 +5720,7 @@
       <c r="E32" s="3"/>
       <c r="F32" s="4"/>
     </row>
-    <row r="33" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A33" s="1"/>
       <c r="B33" s="3"/>
       <c r="C33" s="3"/>
@@ -5907,7 +5728,7 @@
       <c r="E33" s="3"/>
       <c r="F33" s="4"/>
     </row>
-    <row r="34" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A34" s="1"/>
       <c r="B34" s="3"/>
       <c r="C34" s="3"/>
@@ -5923,16 +5744,16 @@
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{46EB2121-1E5C-40E6-84C9-729FC25AD7CB}">
   <dimension ref="A2:L31"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="39.5703125" customWidth="1"/>
-    <col min="2" max="9" width="17.7109375" customWidth="1"/>
-    <col min="10" max="10" width="18.5703125" customWidth="1"/>
-    <col min="11" max="11" width="13.28515625" customWidth="1"/>
-    <col min="12" max="12" width="91.85546875" customWidth="1"/>
+    <col min="1" max="1" width="39.546875" customWidth="1"/>
+    <col min="2" max="9" width="17.75390625" customWidth="1"/>
+    <col min="10" max="10" width="18.5625" customWidth="1"/>
+    <col min="11" max="11" width="13.31640625" customWidth="1"/>
+    <col min="12" max="12" width="91.87890625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A2" s="8" t="s">
         <v>15</v>
       </c>
@@ -5949,12 +5770,12 @@
         <v>5</v>
       </c>
     </row>
-    <row r="3" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
         <v>20</v>
       </c>
     </row>
-    <row r="4" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:12" x14ac:dyDescent="0.2">
       <c r="B4" s="1">
         <v>2014</v>
       </c>
@@ -5986,7 +5807,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="5" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
         <v>12</v>
       </c>
@@ -6019,7 +5840,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="6" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
         <v>11</v>
       </c>
@@ -6048,7 +5869,7 @@
         <v>2047</v>
       </c>
     </row>
-    <row r="7" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
         <v>13</v>
       </c>
@@ -6084,7 +5905,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="8" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
         <v>16</v>
       </c>
@@ -6125,7 +5946,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="9" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:12" x14ac:dyDescent="0.2">
       <c r="B9" s="1"/>
       <c r="C9" s="1"/>
       <c r="D9" s="1"/>
@@ -6136,7 +5957,7 @@
       <c r="I9" s="1"/>
       <c r="J9" s="21"/>
     </row>
-    <row r="10" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A10" t="s">
         <v>7</v>
       </c>
@@ -6169,7 +5990,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="11" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A11" t="s">
         <v>9</v>
       </c>
@@ -6203,7 +6024,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="12" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A12" t="s">
         <v>10</v>
       </c>
@@ -6247,7 +6068,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="13" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A13" t="s">
         <v>28</v>
       </c>
@@ -6291,7 +6112,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="14" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:12" x14ac:dyDescent="0.2">
       <c r="B14" s="9"/>
       <c r="C14" s="9"/>
       <c r="D14" s="9"/>
@@ -6302,7 +6123,7 @@
       <c r="I14" s="9"/>
       <c r="J14" s="5"/>
     </row>
-    <row r="15" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A15" t="s">
         <v>8</v>
       </c>
@@ -6335,7 +6156,7 @@
         <v>92</v>
       </c>
     </row>
-    <row r="16" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A16" t="s">
         <v>21</v>
       </c>
@@ -6376,7 +6197,7 @@
         <v>4.5143647041526519E-3</v>
       </c>
     </row>
-    <row r="17" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A17" t="s">
         <v>59</v>
       </c>
@@ -6409,10 +6230,10 @@
       </c>
       <c r="J17" s="5"/>
       <c r="L17" t="s">
-        <v>115</v>
-      </c>
-    </row>
-    <row r="18" spans="1:12" x14ac:dyDescent="0.25">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="18" spans="1:12" x14ac:dyDescent="0.2">
       <c r="B18" s="9"/>
       <c r="C18" s="9"/>
       <c r="D18" s="9"/>
@@ -6423,7 +6244,7 @@
       <c r="I18" s="9"/>
       <c r="J18" s="5"/>
     </row>
-    <row r="19" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A19" t="s">
         <v>0</v>
       </c>
@@ -6453,7 +6274,7 @@
       </c>
       <c r="J19" s="5"/>
     </row>
-    <row r="20" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A20" t="s">
         <v>1</v>
       </c>
@@ -6495,11 +6316,11 @@
       </c>
       <c r="L20" s="6"/>
     </row>
-    <row r="21" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:12" x14ac:dyDescent="0.2">
       <c r="J21" s="3"/>
       <c r="L21" s="6"/>
     </row>
-    <row r="22" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:12" x14ac:dyDescent="0.2">
       <c r="B22" s="20"/>
       <c r="C22" s="20"/>
       <c r="D22" s="10"/>
@@ -6511,7 +6332,7 @@
       <c r="J22" s="3"/>
       <c r="L22" s="6"/>
     </row>
-    <row r="23" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A23" t="s">
         <v>41</v>
       </c>
@@ -6520,10 +6341,10 @@
         <v>9.4083968122491875E-3</v>
       </c>
       <c r="C23" t="s">
-        <v>130</v>
-      </c>
-    </row>
-    <row r="24" spans="1:12" x14ac:dyDescent="0.25">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="24" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A24" t="s">
         <v>42</v>
       </c>
@@ -6532,10 +6353,10 @@
         <v>7.2428571428571334E-3</v>
       </c>
       <c r="C24" t="s">
-        <v>130</v>
-      </c>
-    </row>
-    <row r="25" spans="1:12" x14ac:dyDescent="0.25">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="25" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A25" t="s">
         <v>27</v>
       </c>
@@ -6544,7 +6365,7 @@
         <v>-2.1655396693920541E-3</v>
       </c>
     </row>
-    <row r="27" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A27" s="1" t="s">
         <v>3</v>
       </c>
@@ -6553,17 +6374,17 @@
         <v>9.408396812249184E-3</v>
       </c>
     </row>
-    <row r="28" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A28" s="1"/>
       <c r="B28" s="21"/>
     </row>
-    <row r="29" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:12" x14ac:dyDescent="0.2">
       <c r="B29" s="5"/>
     </row>
-    <row r="30" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A30" s="1"/>
     </row>
-    <row r="31" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A31" s="1"/>
       <c r="B31" s="21"/>
     </row>
@@ -6575,16 +6396,16 @@
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1F8993B4-587A-4EB9-885B-D46C1E7C06F6}">
   <dimension ref="A2:K32"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="39.5703125" customWidth="1"/>
-    <col min="2" max="8" width="17.7109375" customWidth="1"/>
-    <col min="9" max="9" width="24.7109375" customWidth="1"/>
-    <col min="10" max="10" width="19.140625" customWidth="1"/>
-    <col min="11" max="11" width="91.85546875" customWidth="1"/>
+    <col min="1" max="1" width="39.546875" customWidth="1"/>
+    <col min="2" max="8" width="17.75390625" customWidth="1"/>
+    <col min="9" max="9" width="24.75" customWidth="1"/>
+    <col min="10" max="10" width="19.1015625" customWidth="1"/>
+    <col min="11" max="11" width="91.87890625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A2" s="8" t="s">
         <v>80</v>
       </c>
@@ -6600,7 +6421,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="3" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
         <v>81</v>
       </c>
@@ -6608,7 +6429,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="4" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:11" x14ac:dyDescent="0.2">
       <c r="B4" s="1">
         <v>2015</v>
       </c>
@@ -6637,7 +6458,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="5" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
         <v>12</v>
       </c>
@@ -6664,7 +6485,7 @@
       </c>
       <c r="I5" s="1"/>
     </row>
-    <row r="6" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
         <v>11</v>
       </c>
@@ -6693,7 +6514,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="7" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
         <v>13</v>
       </c>
@@ -6726,7 +6547,7 @@
         <v>89</v>
       </c>
     </row>
-    <row r="8" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
         <v>16</v>
       </c>
@@ -6763,7 +6584,7 @@
         <v>91</v>
       </c>
     </row>
-    <row r="9" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:11" x14ac:dyDescent="0.2">
       <c r="B9" s="1"/>
       <c r="C9" s="1"/>
       <c r="D9" s="1"/>
@@ -6773,7 +6594,7 @@
       <c r="H9" s="1"/>
       <c r="I9" s="5"/>
     </row>
-    <row r="10" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A10" t="s">
         <v>7</v>
       </c>
@@ -6800,10 +6621,10 @@
       </c>
       <c r="I10" s="5"/>
       <c r="K10" t="s">
-        <v>132</v>
-      </c>
-    </row>
-    <row r="11" spans="1:11" x14ac:dyDescent="0.25">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="11" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A11" t="s">
         <v>9</v>
       </c>
@@ -6830,7 +6651,7 @@
       </c>
       <c r="I11" s="5"/>
     </row>
-    <row r="12" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A12" t="s">
         <v>10</v>
       </c>
@@ -6867,10 +6688,10 @@
         <v>0.10486814843192442</v>
       </c>
       <c r="K12" s="44" t="s">
-        <v>117</v>
-      </c>
-    </row>
-    <row r="13" spans="1:11" x14ac:dyDescent="0.25">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="13" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A13" t="s">
         <v>28</v>
       </c>
@@ -6907,7 +6728,7 @@
         <v>3.5658048090037729E-3</v>
       </c>
     </row>
-    <row r="14" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A14" t="s">
         <v>87</v>
       </c>
@@ -6944,7 +6765,7 @@
         <v>3.400771684343195E-2</v>
       </c>
     </row>
-    <row r="15" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:11" x14ac:dyDescent="0.2">
       <c r="B15" s="9"/>
       <c r="C15" s="9"/>
       <c r="D15" s="9"/>
@@ -6954,7 +6775,7 @@
       <c r="H15" s="9"/>
       <c r="I15" s="5"/>
     </row>
-    <row r="16" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A16" t="s">
         <v>8</v>
       </c>
@@ -6981,7 +6802,7 @@
       </c>
       <c r="I16" s="5"/>
     </row>
-    <row r="17" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A17" t="s">
         <v>21</v>
       </c>
@@ -7018,7 +6839,7 @@
         <v>1.8638343141286955E-4</v>
       </c>
     </row>
-    <row r="18" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A18" t="s">
         <v>59</v>
       </c>
@@ -7044,7 +6865,7 @@
       </c>
       <c r="I18" s="5"/>
     </row>
-    <row r="19" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:11" x14ac:dyDescent="0.2">
       <c r="B19" s="9"/>
       <c r="C19" s="9"/>
       <c r="D19" s="9"/>
@@ -7054,7 +6875,7 @@
       <c r="H19" s="9"/>
       <c r="I19" s="5"/>
     </row>
-    <row r="20" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A20" t="s">
         <v>0</v>
       </c>
@@ -7079,7 +6900,7 @@
       </c>
       <c r="I20" s="5"/>
     </row>
-    <row r="21" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A21" t="s">
         <v>1</v>
       </c>
@@ -7114,11 +6935,11 @@
       </c>
       <c r="K21" s="6"/>
     </row>
-    <row r="22" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:11" x14ac:dyDescent="0.2">
       <c r="I22" s="3"/>
       <c r="K22" s="6"/>
     </row>
-    <row r="23" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:11" x14ac:dyDescent="0.2">
       <c r="B23" s="20"/>
       <c r="C23" s="20"/>
       <c r="D23" s="10"/>
@@ -7129,7 +6950,7 @@
       <c r="I23" s="3"/>
       <c r="K23" s="6"/>
     </row>
-    <row r="24" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A24" t="s">
         <v>41</v>
       </c>
@@ -7138,10 +6959,10 @@
         <v>7.475595000300852E-3</v>
       </c>
       <c r="C24" t="s">
-        <v>127</v>
-      </c>
-    </row>
-    <row r="25" spans="1:11" x14ac:dyDescent="0.25">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="25" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A25" t="s">
         <v>42</v>
       </c>
@@ -7150,10 +6971,10 @@
         <v>6.6166666666666622E-3</v>
       </c>
       <c r="C25" t="s">
-        <v>127</v>
-      </c>
-    </row>
-    <row r="26" spans="1:11" x14ac:dyDescent="0.25">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="26" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A26" t="s">
         <v>27</v>
       </c>
@@ -7162,7 +6983,7 @@
         <v>-8.5892833363418984E-4</v>
       </c>
     </row>
-    <row r="28" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A28" s="1" t="s">
         <v>3</v>
       </c>
@@ -7171,17 +6992,17 @@
         <v>7.6617011843167155E-3</v>
       </c>
     </row>
-    <row r="29" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A29" s="1"/>
       <c r="B29" s="21"/>
     </row>
-    <row r="30" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:11" x14ac:dyDescent="0.2">
       <c r="B30" s="5"/>
     </row>
-    <row r="31" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A31" s="1"/>
     </row>
-    <row r="32" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A32" s="1"/>
       <c r="B32" s="21"/>
     </row>
@@ -7193,14 +7014,14 @@
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4ABDDF6C-AD69-4170-ABB3-6C33D8EBF3CF}">
   <dimension ref="A2:N27"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="41.140625" bestFit="1" customWidth="1"/>
-    <col min="2" max="10" width="8.7109375" customWidth="1"/>
-    <col min="12" max="12" width="15.85546875" customWidth="1"/>
+    <col min="1" max="1" width="41.1640625" bestFit="1" customWidth="1"/>
+    <col min="2" max="10" width="8.7421875" customWidth="1"/>
+    <col min="12" max="12" width="15.87109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A2" s="1" t="s">
         <v>99</v>
       </c>
@@ -7229,10 +7050,10 @@
         <v>104</v>
       </c>
       <c r="L2" t="s">
-        <v>143</v>
-      </c>
-    </row>
-    <row r="3" spans="1:14" x14ac:dyDescent="0.25">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="3" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
         <v>90</v>
       </c>
@@ -7258,7 +7079,7 @@
         <v>78113</v>
       </c>
     </row>
-    <row r="4" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
         <v>100</v>
       </c>
@@ -7284,7 +7105,7 @@
         <v>1663</v>
       </c>
     </row>
-    <row r="5" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
         <v>105</v>
       </c>
@@ -7321,16 +7142,16 @@
         <v>2.0655550077951876E-2</v>
       </c>
     </row>
-    <row r="6" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:14" x14ac:dyDescent="0.2">
       <c r="J6" s="5"/>
     </row>
-    <row r="7" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A7" s="1" t="s">
         <v>101</v>
       </c>
       <c r="J7" s="5"/>
     </row>
-    <row r="8" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
         <v>90</v>
       </c>
@@ -7357,10 +7178,10 @@
       </c>
       <c r="J8" s="5"/>
       <c r="L8" t="s">
-        <v>143</v>
-      </c>
-    </row>
-    <row r="9" spans="1:14" x14ac:dyDescent="0.25">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="9" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
         <v>100</v>
       </c>
@@ -7387,7 +7208,7 @@
       </c>
       <c r="J9" s="5"/>
     </row>
-    <row r="10" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A10" t="s">
         <v>105</v>
       </c>
@@ -7424,11 +7245,11 @@
         <v>0.25081285336016573</v>
       </c>
     </row>
-    <row r="11" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:14" x14ac:dyDescent="0.2">
       <c r="J11" s="5"/>
       <c r="M11" s="43"/>
     </row>
-    <row r="12" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A12" s="1" t="s">
         <v>102</v>
       </c>
@@ -7436,7 +7257,7 @@
       <c r="M12" s="43"/>
       <c r="N12" s="5"/>
     </row>
-    <row r="13" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A13" t="s">
         <v>90</v>
       </c>
@@ -7463,12 +7284,12 @@
       </c>
       <c r="J13" s="5"/>
       <c r="L13" t="s">
-        <v>143</v>
+        <v>130</v>
       </c>
       <c r="M13" s="43"/>
       <c r="N13" s="5"/>
     </row>
-    <row r="14" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A14" t="s">
         <v>100</v>
       </c>
@@ -7496,7 +7317,7 @@
       <c r="J14" s="5"/>
       <c r="N14" s="5"/>
     </row>
-    <row r="15" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A15" t="s">
         <v>105</v>
       </c>
@@ -7533,16 +7354,16 @@
         <v>0.14908378682768386</v>
       </c>
     </row>
-    <row r="16" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:14" x14ac:dyDescent="0.2">
       <c r="J16" s="5"/>
     </row>
-    <row r="17" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A17" s="1" t="s">
         <v>103</v>
       </c>
       <c r="J17" s="5"/>
     </row>
-    <row r="18" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A18" t="s">
         <v>90</v>
       </c>
@@ -7569,10 +7390,10 @@
       </c>
       <c r="J18" s="5"/>
       <c r="L18" t="s">
-        <v>143</v>
-      </c>
-    </row>
-    <row r="19" spans="1:12" x14ac:dyDescent="0.25">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="19" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A19" t="s">
         <v>100</v>
       </c>
@@ -7599,7 +7420,7 @@
       </c>
       <c r="J19" s="5"/>
     </row>
-    <row r="20" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A20" t="s">
         <v>105</v>
       </c>
@@ -7636,16 +7457,16 @@
         <v>0.14293551855049416</v>
       </c>
     </row>
-    <row r="21" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:12" x14ac:dyDescent="0.2">
       <c r="J21" s="5"/>
     </row>
-    <row r="22" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A22" s="1" t="s">
         <v>106</v>
       </c>
       <c r="J22" s="5"/>
     </row>
-    <row r="23" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A23" t="s">
         <v>90</v>
       </c>
@@ -7672,10 +7493,10 @@
       </c>
       <c r="J23" s="5"/>
       <c r="L23" t="s">
-        <v>144</v>
-      </c>
-    </row>
-    <row r="24" spans="1:12" x14ac:dyDescent="0.25">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="24" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A24" t="s">
         <v>100</v>
       </c>
@@ -7702,7 +7523,7 @@
       </c>
       <c r="J24" s="5"/>
     </row>
-    <row r="25" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A25" t="s">
         <v>105</v>
       </c>
@@ -7739,7 +7560,7 @@
         <v>7.7066032445956917E-2</v>
       </c>
     </row>
-    <row r="27" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A27" t="s">
         <v>107</v>
       </c>

--- a/iShares/iShares-costs.xlsx
+++ b/iShares/iShares-costs.xlsx
@@ -1,29 +1,30 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29328"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29426"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/7c741cee80ec8cf3/Financieel/IndexFondsenOnderzoek/KeuzeWelkIndexFonds/OnderzoekPerFonds/iShares/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1848" documentId="13_ncr:1_{A6ACE176-4C08-4AFF-ACEF-0847542540D3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{B49FDF2A-9A46-4CF9-9ADB-3B08C8FB38B2}"/>
+  <xr:revisionPtr revIDLastSave="1957" documentId="13_ncr:1_{A6ACE176-4C08-4AFF-ACEF-0847542540D3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{BAF53A48-7147-4E6B-9912-69485ABD31C6}"/>
   <bookViews>
-    <workbookView xWindow="-105" yWindow="0" windowWidth="26010" windowHeight="20985" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="25695" yWindow="0" windowWidth="26010" windowHeight="20985" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Aanames" sheetId="6" r:id="rId1"/>
     <sheet name="IWDA" sheetId="1" r:id="rId2"/>
-    <sheet name="EMIM" sheetId="4" r:id="rId3"/>
-    <sheet name="IEMA" sheetId="11" r:id="rId4"/>
-    <sheet name="WSML" sheetId="3" r:id="rId5"/>
-    <sheet name="IEMS" sheetId="2" r:id="rId6"/>
-    <sheet name="Dividendlek" sheetId="14" r:id="rId7"/>
-    <sheet name="TrackingDifference" sheetId="5" r:id="rId8"/>
-    <sheet name="Lending%" sheetId="13" r:id="rId9"/>
-    <sheet name="arh-IEMM" sheetId="9" r:id="rId10"/>
-    <sheet name="arch-IWVL" sheetId="12" r:id="rId11"/>
+    <sheet name="SSAC" sheetId="15" r:id="rId3"/>
+    <sheet name="EMIM" sheetId="4" r:id="rId4"/>
+    <sheet name="IEMA" sheetId="11" r:id="rId5"/>
+    <sheet name="WSML" sheetId="3" r:id="rId6"/>
+    <sheet name="IEMS" sheetId="2" r:id="rId7"/>
+    <sheet name="Dividendlek" sheetId="14" r:id="rId8"/>
+    <sheet name="TrackingDifference" sheetId="5" r:id="rId9"/>
+    <sheet name="Lending%" sheetId="13" r:id="rId10"/>
+    <sheet name="arh-IEMM" sheetId="9" r:id="rId11"/>
+    <sheet name="arch-IWVL" sheetId="12" r:id="rId12"/>
   </sheets>
   <calcPr calcId="191028" concurrentCalc="0"/>
   <extLst>
@@ -286,7 +287,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="328" uniqueCount="154">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="344" uniqueCount="157">
   <si>
     <t>Transaction costs</t>
   </si>
@@ -748,6 +749,15 @@
   </si>
   <si>
     <t>KID % transaction costs</t>
+  </si>
+  <si>
+    <t>iShares MSCI ACWI UCITS ETF (SSAC)</t>
+  </si>
+  <si>
+    <t>Remarks</t>
+  </si>
+  <si>
+    <t>For the financial year ended 30 November</t>
   </si>
 </sst>
 </file>
@@ -942,7 +952,7 @@
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="10" fontId="0" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
     <xf numFmtId="164" fontId="2" fillId="0" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="10" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
+    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="4">
     <cellStyle name="Comma" xfId="3" builtinId="3"/>
@@ -1288,6 +1298,145 @@
 </file>
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1DB4ADDA-011E-42C7-847A-CF64D6C09BA3}">
+  <dimension ref="B1:D12"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetData>
+    <row r="1" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="C1" t="s">
+        <v>90</v>
+      </c>
+      <c r="D1" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="2" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B2">
+        <v>2014</v>
+      </c>
+      <c r="C2">
+        <v>60</v>
+      </c>
+      <c r="D2">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="3" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B3">
+        <v>2015</v>
+      </c>
+      <c r="C3">
+        <v>62.5</v>
+      </c>
+      <c r="D3">
+        <v>37.5</v>
+      </c>
+    </row>
+    <row r="4" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B4">
+        <v>2016</v>
+      </c>
+      <c r="C4">
+        <v>62.5</v>
+      </c>
+      <c r="D4">
+        <v>37.5</v>
+      </c>
+    </row>
+    <row r="5" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B5">
+        <v>2017</v>
+      </c>
+      <c r="C5">
+        <v>62.5</v>
+      </c>
+      <c r="D5">
+        <v>37.5</v>
+      </c>
+    </row>
+    <row r="6" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B6">
+        <v>2018</v>
+      </c>
+      <c r="C6">
+        <v>62.5</v>
+      </c>
+      <c r="D6">
+        <v>37.5</v>
+      </c>
+    </row>
+    <row r="7" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B7">
+        <v>2019</v>
+      </c>
+      <c r="C7">
+        <v>62.5</v>
+      </c>
+      <c r="D7">
+        <v>37.5</v>
+      </c>
+    </row>
+    <row r="8" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B8">
+        <v>2020</v>
+      </c>
+      <c r="C8">
+        <v>62.5</v>
+      </c>
+      <c r="D8">
+        <v>37.5</v>
+      </c>
+    </row>
+    <row r="9" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B9">
+        <v>2021</v>
+      </c>
+      <c r="C9">
+        <v>62.5</v>
+      </c>
+      <c r="D9">
+        <v>37.5</v>
+      </c>
+    </row>
+    <row r="10" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B10">
+        <v>2022</v>
+      </c>
+      <c r="C10">
+        <v>62.5</v>
+      </c>
+      <c r="D10">
+        <v>37.5</v>
+      </c>
+    </row>
+    <row r="11" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B11">
+        <v>2023</v>
+      </c>
+      <c r="C11">
+        <v>62.5</v>
+      </c>
+      <c r="D11">
+        <v>37.5</v>
+      </c>
+    </row>
+    <row r="12" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B12">
+        <v>2024</v>
+      </c>
+      <c r="C12">
+        <v>62.5</v>
+      </c>
+      <c r="D12">
+        <v>37.5</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1C9A39DF-ECA7-4B8A-BED1-414B316C3BE0}">
   <dimension ref="A2:M31"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -1974,7 +2123,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1F8993B4-587A-4EB9-885B-D46C1E7C06F6}">
   <dimension ref="A2:K32"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -3750,6 +3899,425 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9A84F525-ACA9-4457-B165-3A41133FFD52}">
+  <dimension ref="A2:O37"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="36.42578125" customWidth="1"/>
+    <col min="2" max="8" width="17.7109375" customWidth="1"/>
+    <col min="9" max="9" width="13.28515625" customWidth="1"/>
+    <col min="13" max="13" width="13.7109375" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="9.85546875" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="2" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A2" s="8" t="s">
+        <v>154</v>
+      </c>
+      <c r="B2" s="8"/>
+      <c r="C2" s="8"/>
+      <c r="D2" s="8"/>
+      <c r="E2" s="8"/>
+      <c r="F2" s="7"/>
+      <c r="G2" s="7"/>
+      <c r="H2" s="7"/>
+      <c r="I2" s="7"/>
+      <c r="K2" t="s">
+        <v>155</v>
+      </c>
+    </row>
+    <row r="4" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="B4" s="1">
+        <v>2019</v>
+      </c>
+      <c r="C4" s="1">
+        <v>2020</v>
+      </c>
+      <c r="D4" s="1">
+        <v>2021</v>
+      </c>
+      <c r="E4" s="1">
+        <v>2022</v>
+      </c>
+      <c r="F4" s="1">
+        <v>2023</v>
+      </c>
+      <c r="G4" s="1">
+        <v>2024</v>
+      </c>
+      <c r="H4" s="1">
+        <v>2025</v>
+      </c>
+      <c r="I4" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="K4" t="s">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="5" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
+        <v>11</v>
+      </c>
+      <c r="E5" s="15">
+        <v>10237</v>
+      </c>
+      <c r="F5" s="15">
+        <v>15243</v>
+      </c>
+      <c r="G5" s="16">
+        <v>27222</v>
+      </c>
+      <c r="H5" s="16"/>
+    </row>
+    <row r="6" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
+        <v>136</v>
+      </c>
+      <c r="E6" s="17">
+        <v>2E-3</v>
+      </c>
+      <c r="F6" s="17">
+        <v>2E-3</v>
+      </c>
+      <c r="G6" s="17">
+        <v>2E-3</v>
+      </c>
+      <c r="H6" s="17"/>
+    </row>
+    <row r="7" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A7" t="s">
+        <v>135</v>
+      </c>
+      <c r="E7" s="15">
+        <v>6071464</v>
+      </c>
+      <c r="F7" s="15">
+        <v>9796139</v>
+      </c>
+      <c r="G7" s="15">
+        <v>17433095</v>
+      </c>
+      <c r="H7" s="17"/>
+    </row>
+    <row r="8" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A8" t="s">
+        <v>137</v>
+      </c>
+      <c r="E8" s="16">
+        <f>E5/E6</f>
+        <v>5118500</v>
+      </c>
+      <c r="F8" s="16">
+        <f>F5/F6</f>
+        <v>7621500</v>
+      </c>
+      <c r="G8" s="16">
+        <f>G5/G6</f>
+        <v>13611000</v>
+      </c>
+      <c r="H8" s="16"/>
+    </row>
+    <row r="9" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="E9" s="16"/>
+      <c r="F9" s="16"/>
+      <c r="G9" s="16"/>
+      <c r="H9" s="16"/>
+    </row>
+    <row r="10" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A10" t="s">
+        <v>7</v>
+      </c>
+      <c r="B10" s="16">
+        <v>18613</v>
+      </c>
+      <c r="C10" s="16">
+        <v>21073</v>
+      </c>
+      <c r="D10" s="16">
+        <v>45981</v>
+      </c>
+      <c r="E10" s="16">
+        <v>109141</v>
+      </c>
+      <c r="F10" s="16">
+        <v>164284</v>
+      </c>
+      <c r="G10" s="16">
+        <v>256848</v>
+      </c>
+      <c r="H10" s="16"/>
+    </row>
+    <row r="11" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A11" t="s">
+        <v>138</v>
+      </c>
+      <c r="B11" s="16">
+        <v>2297</v>
+      </c>
+      <c r="C11" s="16">
+        <v>2745</v>
+      </c>
+      <c r="D11" s="16">
+        <v>5401</v>
+      </c>
+      <c r="E11" s="16">
+        <v>13293</v>
+      </c>
+      <c r="F11" s="16">
+        <v>19962</v>
+      </c>
+      <c r="G11" s="16">
+        <v>30745</v>
+      </c>
+      <c r="H11" s="16"/>
+    </row>
+    <row r="12" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A12" t="s">
+        <v>139</v>
+      </c>
+      <c r="B12" s="11">
+        <f>B11/B10</f>
+        <v>0.12340837049374094</v>
+      </c>
+      <c r="C12" s="11">
+        <f t="shared" ref="C12:G12" si="0">C11/C10</f>
+        <v>0.13026147202581503</v>
+      </c>
+      <c r="D12" s="11">
+        <f t="shared" si="0"/>
+        <v>0.11746156020965182</v>
+      </c>
+      <c r="E12" s="11">
+        <f t="shared" si="0"/>
+        <v>0.12179657507261249</v>
+      </c>
+      <c r="F12" s="11">
+        <f t="shared" si="0"/>
+        <v>0.12150909400793747</v>
+      </c>
+      <c r="G12" s="11">
+        <f t="shared" si="0"/>
+        <v>0.11970114620320189</v>
+      </c>
+      <c r="H12" s="20"/>
+      <c r="I12" s="47">
+        <f>AVERAGE(B12:G12)</f>
+        <v>0.12235636966882663</v>
+      </c>
+    </row>
+    <row r="13" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="E13" s="16"/>
+      <c r="F13" s="16"/>
+      <c r="G13" s="16"/>
+      <c r="H13" s="16"/>
+    </row>
+    <row r="14" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A14" t="s">
+        <v>8</v>
+      </c>
+      <c r="E14" s="15">
+        <v>1603</v>
+      </c>
+      <c r="F14" s="15">
+        <v>1880</v>
+      </c>
+      <c r="G14" s="16">
+        <v>2934</v>
+      </c>
+      <c r="H14" s="16"/>
+    </row>
+    <row r="15" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A15" t="s">
+        <v>21</v>
+      </c>
+      <c r="E15" s="38">
+        <f>E14/E8</f>
+        <v>3.131776887760086E-4</v>
+      </c>
+      <c r="F15" s="38">
+        <f>F14/F8</f>
+        <v>2.4667060289969165E-4</v>
+      </c>
+      <c r="G15" s="38">
+        <f>G14/G8</f>
+        <v>2.1556094335463963E-4</v>
+      </c>
+      <c r="H15" s="38"/>
+    </row>
+    <row r="16" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="E16" s="15"/>
+      <c r="F16" s="15"/>
+      <c r="G16" s="16"/>
+      <c r="H16" s="16"/>
+    </row>
+    <row r="17" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="E17" s="20"/>
+      <c r="F17" s="20"/>
+      <c r="G17" s="20"/>
+      <c r="H17" s="20"/>
+    </row>
+    <row r="18" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A18" t="s">
+        <v>153</v>
+      </c>
+      <c r="H18" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="20" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="E20" s="5"/>
+      <c r="G20" s="10"/>
+      <c r="H20" s="10"/>
+      <c r="M20" s="5"/>
+    </row>
+    <row r="21" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A21" s="1" t="s">
+        <v>145</v>
+      </c>
+      <c r="B21" s="1"/>
+      <c r="C21" s="1"/>
+      <c r="D21" s="1"/>
+      <c r="M21" s="39"/>
+    </row>
+    <row r="22" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A22" t="s">
+        <v>147</v>
+      </c>
+      <c r="E22" s="4">
+        <f>AVERAGE(E15:G15)</f>
+        <v>2.5846974501011333E-4</v>
+      </c>
+    </row>
+    <row r="23" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="I23" s="4"/>
+    </row>
+    <row r="24" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A24" s="1"/>
+      <c r="B24" s="1"/>
+      <c r="C24" s="1"/>
+      <c r="D24" s="1"/>
+      <c r="E24" s="10"/>
+      <c r="I24" s="4"/>
+    </row>
+    <row r="25" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="I25" s="4"/>
+    </row>
+    <row r="26" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="I26" s="4"/>
+    </row>
+    <row r="27" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="E27" s="4"/>
+      <c r="F27" s="10"/>
+      <c r="G27" s="10"/>
+      <c r="H27" s="10"/>
+      <c r="I27" s="4"/>
+      <c r="M27" s="2"/>
+      <c r="O27" s="40"/>
+    </row>
+    <row r="28" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="E28" s="4"/>
+      <c r="F28" s="10"/>
+      <c r="G28" s="10"/>
+      <c r="H28" s="10"/>
+      <c r="I28" s="4"/>
+    </row>
+    <row r="29" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="F29" s="10"/>
+      <c r="G29" s="10"/>
+      <c r="H29" s="10"/>
+      <c r="I29" s="4"/>
+    </row>
+    <row r="30" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="E30" s="4"/>
+      <c r="F30" s="10"/>
+      <c r="G30" s="10"/>
+      <c r="H30" s="10"/>
+      <c r="I30" s="4"/>
+    </row>
+    <row r="31" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A31" s="1"/>
+      <c r="B31" s="1"/>
+      <c r="C31" s="1"/>
+      <c r="D31" s="1"/>
+      <c r="E31" s="21"/>
+      <c r="F31" s="10"/>
+      <c r="G31" s="10"/>
+      <c r="H31" s="10"/>
+      <c r="I31" s="4"/>
+    </row>
+    <row r="32" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A32" s="1"/>
+      <c r="B32" s="1"/>
+      <c r="C32" s="1"/>
+      <c r="D32" s="1"/>
+      <c r="E32" s="1"/>
+      <c r="F32" s="10"/>
+      <c r="G32" s="10"/>
+      <c r="H32" s="10"/>
+      <c r="I32" s="4"/>
+    </row>
+    <row r="33" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A33" s="1"/>
+      <c r="B33" s="1"/>
+      <c r="C33" s="1"/>
+      <c r="D33" s="1"/>
+      <c r="E33" s="1"/>
+      <c r="F33" s="10"/>
+      <c r="G33" s="10"/>
+      <c r="H33" s="10"/>
+      <c r="I33" s="4"/>
+    </row>
+    <row r="34" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A34" s="1"/>
+      <c r="B34" s="1"/>
+      <c r="C34" s="1"/>
+      <c r="D34" s="1"/>
+      <c r="E34" s="1"/>
+      <c r="F34" s="10"/>
+      <c r="G34" s="10"/>
+      <c r="H34" s="10"/>
+      <c r="I34" s="4"/>
+    </row>
+    <row r="35" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A35" s="1"/>
+      <c r="B35" s="1"/>
+      <c r="C35" s="1"/>
+      <c r="D35" s="1"/>
+      <c r="E35" s="1"/>
+      <c r="F35" s="10"/>
+      <c r="G35" s="10"/>
+      <c r="H35" s="10"/>
+      <c r="I35" s="4"/>
+    </row>
+    <row r="36" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A36" s="1"/>
+      <c r="B36" s="1"/>
+      <c r="C36" s="1"/>
+      <c r="D36" s="1"/>
+      <c r="E36" s="1"/>
+      <c r="F36" s="10"/>
+      <c r="G36" s="10"/>
+      <c r="H36" s="10"/>
+      <c r="I36" s="4"/>
+    </row>
+    <row r="37" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A37" s="1"/>
+      <c r="B37" s="1"/>
+      <c r="C37" s="1"/>
+      <c r="D37" s="1"/>
+      <c r="E37" s="1"/>
+      <c r="F37" s="10"/>
+      <c r="G37" s="10"/>
+      <c r="H37" s="10"/>
+      <c r="I37" s="4"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{85662431-B8A3-40F8-9BF4-EC97DECEFC14}">
   <dimension ref="A2:O34"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -4557,7 +5125,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CF4E9972-EF6D-435D-B893-B5209367B0F1}">
   <dimension ref="A2:P34"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -5381,7 +5949,7 @@
       <c r="A26" t="s">
         <v>144</v>
       </c>
-      <c r="B26" s="47">
+      <c r="B26" s="5">
         <f>B25-B24</f>
         <v>-3.3702448885587072E-4</v>
       </c>
@@ -5446,7 +6014,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3319A48F-C74C-4C2A-9714-F1A50A94B19B}">
   <dimension ref="A2:K35"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -6135,7 +6703,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{46EB2121-1E5C-40E6-84C9-729FC25AD7CB}">
   <dimension ref="A2:P34"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -6712,7 +7280,7 @@
         <v>3.2701707398727822E-3</v>
       </c>
       <c r="D16" s="14">
-        <f t="shared" ref="D16:L16" si="3">D15/D8</f>
+        <f t="shared" ref="D16:K16" si="3">D15/D8</f>
         <v>4.9717587939698488E-3</v>
       </c>
       <c r="E16" s="14">
@@ -7042,7 +7610,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4ABDDF6C-AD69-4170-ABB3-6C33D8EBF3CF}">
   <dimension ref="A2:N27"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -7606,7 +8174,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{045330D2-0890-4532-8ABA-CDB206A2E066}">
   <dimension ref="B1:T56"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -9221,143 +9789,4 @@
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <legacyDrawing r:id="rId1"/>
 </worksheet>
-</file>
-
-<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1DB4ADDA-011E-42C7-847A-CF64D6C09BA3}">
-  <dimension ref="B1:D12"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
-  <sheetData>
-    <row r="1" spans="2:4" x14ac:dyDescent="0.25">
-      <c r="C1" t="s">
-        <v>90</v>
-      </c>
-      <c r="D1" t="s">
-        <v>91</v>
-      </c>
-    </row>
-    <row r="2" spans="2:4" x14ac:dyDescent="0.25">
-      <c r="B2">
-        <v>2014</v>
-      </c>
-      <c r="C2">
-        <v>60</v>
-      </c>
-      <c r="D2">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="3" spans="2:4" x14ac:dyDescent="0.25">
-      <c r="B3">
-        <v>2015</v>
-      </c>
-      <c r="C3">
-        <v>62.5</v>
-      </c>
-      <c r="D3">
-        <v>37.5</v>
-      </c>
-    </row>
-    <row r="4" spans="2:4" x14ac:dyDescent="0.25">
-      <c r="B4">
-        <v>2016</v>
-      </c>
-      <c r="C4">
-        <v>62.5</v>
-      </c>
-      <c r="D4">
-        <v>37.5</v>
-      </c>
-    </row>
-    <row r="5" spans="2:4" x14ac:dyDescent="0.25">
-      <c r="B5">
-        <v>2017</v>
-      </c>
-      <c r="C5">
-        <v>62.5</v>
-      </c>
-      <c r="D5">
-        <v>37.5</v>
-      </c>
-    </row>
-    <row r="6" spans="2:4" x14ac:dyDescent="0.25">
-      <c r="B6">
-        <v>2018</v>
-      </c>
-      <c r="C6">
-        <v>62.5</v>
-      </c>
-      <c r="D6">
-        <v>37.5</v>
-      </c>
-    </row>
-    <row r="7" spans="2:4" x14ac:dyDescent="0.25">
-      <c r="B7">
-        <v>2019</v>
-      </c>
-      <c r="C7">
-        <v>62.5</v>
-      </c>
-      <c r="D7">
-        <v>37.5</v>
-      </c>
-    </row>
-    <row r="8" spans="2:4" x14ac:dyDescent="0.25">
-      <c r="B8">
-        <v>2020</v>
-      </c>
-      <c r="C8">
-        <v>62.5</v>
-      </c>
-      <c r="D8">
-        <v>37.5</v>
-      </c>
-    </row>
-    <row r="9" spans="2:4" x14ac:dyDescent="0.25">
-      <c r="B9">
-        <v>2021</v>
-      </c>
-      <c r="C9">
-        <v>62.5</v>
-      </c>
-      <c r="D9">
-        <v>37.5</v>
-      </c>
-    </row>
-    <row r="10" spans="2:4" x14ac:dyDescent="0.25">
-      <c r="B10">
-        <v>2022</v>
-      </c>
-      <c r="C10">
-        <v>62.5</v>
-      </c>
-      <c r="D10">
-        <v>37.5</v>
-      </c>
-    </row>
-    <row r="11" spans="2:4" x14ac:dyDescent="0.25">
-      <c r="B11">
-        <v>2023</v>
-      </c>
-      <c r="C11">
-        <v>62.5</v>
-      </c>
-      <c r="D11">
-        <v>37.5</v>
-      </c>
-    </row>
-    <row r="12" spans="2:4" x14ac:dyDescent="0.25">
-      <c r="B12">
-        <v>2024</v>
-      </c>
-      <c r="C12">
-        <v>62.5</v>
-      </c>
-      <c r="D12">
-        <v>37.5</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
 </file>
--- a/iShares/iShares-costs.xlsx
+++ b/iShares/iShares-costs.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/7c741cee80ec8cf3/Financieel/IndexFondsenOnderzoek/KeuzeWelkIndexFonds/OnderzoekPerFonds/iShares/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1957" documentId="13_ncr:1_{A6ACE176-4C08-4AFF-ACEF-0847542540D3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{BAF53A48-7147-4E6B-9912-69485ABD31C6}"/>
+  <xr:revisionPtr revIDLastSave="1963" documentId="13_ncr:1_{A6ACE176-4C08-4AFF-ACEF-0847542540D3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{A849EAC6-E880-4A13-A48A-D44EF6F07155}"/>
   <bookViews>
-    <workbookView xWindow="25695" yWindow="0" windowWidth="26010" windowHeight="20985" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="25695" yWindow="0" windowWidth="26010" windowHeight="20985" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Aanames" sheetId="6" r:id="rId1"/>
@@ -973,10 +973,6 @@
 </styleSheet>
 </file>
 
-<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
-<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
-</file>
-
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
 <a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
   <a:themeElements>

--- a/iShares/iShares-costs.xlsx
+++ b/iShares/iShares-costs.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29426"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29929"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/7c741cee80ec8cf3/Financieel/IndexFondsenOnderzoek/KeuzeWelkIndexFonds/OnderzoekPerFonds/iShares/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1963" documentId="13_ncr:1_{A6ACE176-4C08-4AFF-ACEF-0847542540D3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{A849EAC6-E880-4A13-A48A-D44EF6F07155}"/>
+  <xr:revisionPtr revIDLastSave="1973" documentId="13_ncr:1_{A6ACE176-4C08-4AFF-ACEF-0847542540D3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{7C920088-669F-485C-94FC-A9A72554FA2F}"/>
   <bookViews>
-    <workbookView xWindow="25695" yWindow="0" windowWidth="26010" windowHeight="20985" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="25695" yWindow="0" windowWidth="26010" windowHeight="20985" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Aanames" sheetId="6" r:id="rId1"/>
@@ -5055,6 +5055,7 @@
         <f>B25-B24</f>
         <v>-5.7820416708628374E-4</v>
       </c>
+      <c r="J26" s="3"/>
     </row>
     <row r="28" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A28" s="1"/>
